--- a/results/modelling/metrics_summary_all_models.xlsx
+++ b/results/modelling/metrics_summary_all_models.xlsx
@@ -483,28 +483,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6346146790585785</v>
+        <v>0.8085139113098889</v>
       </c>
       <c r="C2" t="n">
-        <v>1.994448000943118</v>
+        <v>1.355803109305723</v>
       </c>
       <c r="D2" t="n">
-        <v>34.42047651773893</v>
+        <v>18.03860757802122</v>
       </c>
       <c r="E2" t="n">
-        <v>5.866896668404765</v>
+        <v>4.24718819668039</v>
       </c>
       <c r="F2" t="n">
-        <v>484.3724338470467</v>
+        <v>247.2439123848417</v>
       </c>
       <c r="G2" t="n">
-        <v>24.20394915869968</v>
+        <v>12.68447113122189</v>
       </c>
       <c r="H2" t="n">
-        <v>1807.480423988822</v>
+        <v>1481.827220506472</v>
       </c>
       <c r="I2" t="n">
-        <v>1858.151339205678</v>
+        <v>1532.498135723328</v>
       </c>
     </row>
     <row r="3">
@@ -514,28 +514,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9232109922110809</v>
+        <v>0.9246009932515711</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8846294500927255</v>
+        <v>0.8509043639312235</v>
       </c>
       <c r="D3" t="n">
-        <v>7.233772371065515</v>
+        <v>7.102829786808017</v>
       </c>
       <c r="E3" t="n">
-        <v>2.68956732041894</v>
+        <v>2.665113466028795</v>
       </c>
       <c r="F3" t="n">
-        <v>51.19551022155618</v>
+        <v>40.58835968631103</v>
       </c>
       <c r="G3" t="n">
-        <v>5.086677362082535</v>
+        <v>4.99460055279014</v>
       </c>
       <c r="H3" t="n">
-        <v>1021.295375914497</v>
+        <v>1012.08860614715</v>
       </c>
       <c r="I3" t="n">
-        <v>1071.966291131354</v>
+        <v>1062.759521364006</v>
       </c>
     </row>
     <row r="4">
@@ -545,28 +545,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9274268851447409</v>
+        <v>0.9275920116120691</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8236408831019392</v>
+        <v>0.8106560840382336</v>
       </c>
       <c r="D4" t="n">
-        <v>6.83662164987491</v>
+        <v>6.821066203705157</v>
       </c>
       <c r="E4" t="n">
-        <v>2.614693414126197</v>
+        <v>2.611717098712102</v>
       </c>
       <c r="F4" t="n">
-        <v>31.88667443426031</v>
+        <v>27.74789787998624</v>
       </c>
       <c r="G4" t="n">
-        <v>4.807407089369015</v>
+        <v>4.796468739109989</v>
       </c>
       <c r="H4" t="n">
-        <v>992.8360241867946</v>
+        <v>991.6879604232016</v>
       </c>
       <c r="I4" t="n">
-        <v>1043.506939403651</v>
+        <v>1042.358875640058</v>
       </c>
     </row>
     <row r="5">
@@ -576,28 +576,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9266329626969777</v>
+        <v>0.927575977998466</v>
       </c>
       <c r="C5" t="n">
-        <v>0.847951777480264</v>
+        <v>0.8120829982730866</v>
       </c>
       <c r="D5" t="n">
-        <v>6.91141170684746</v>
+        <v>6.822576621855221</v>
       </c>
       <c r="E5" t="n">
-        <v>2.628956391203068</v>
+        <v>2.612006244604944</v>
       </c>
       <c r="F5" t="n">
-        <v>41.38381871886968</v>
+        <v>29.39809040691511</v>
       </c>
       <c r="G5" t="n">
-        <v>4.859998305984129</v>
+        <v>4.797530841899115</v>
       </c>
       <c r="H5" t="n">
-        <v>998.3196536755795</v>
+        <v>991.7995509654747</v>
       </c>
       <c r="I5" t="n">
-        <v>1048.990568892436</v>
+        <v>1042.470466182331</v>
       </c>
     </row>
     <row r="6">
@@ -607,28 +607,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9274392017670114</v>
+        <v>0.9276148990918043</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8135984283814214</v>
+        <v>0.8049149790896489</v>
       </c>
       <c r="D6" t="n">
-        <v>6.835461384304999</v>
+        <v>6.818910129244501</v>
       </c>
       <c r="E6" t="n">
-        <v>2.614471530597532</v>
+        <v>2.611304296562257</v>
       </c>
       <c r="F6" t="n">
-        <v>29.48652002652011</v>
+        <v>26.55153827105423</v>
       </c>
       <c r="G6" t="n">
-        <v>4.806591208483395</v>
+        <v>4.794952620743609</v>
       </c>
       <c r="H6" t="n">
-        <v>992.7504814282877</v>
+        <v>991.5286256104871</v>
       </c>
       <c r="I6" t="n">
-        <v>1043.421396645144</v>
+        <v>1042.199540827344</v>
       </c>
     </row>
     <row r="7">
@@ -638,28 +638,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.926992459812655</v>
+        <v>0.92761410533116</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8283520736562779</v>
+        <v>0.8054006869949294</v>
       </c>
       <c r="D7" t="n">
-        <v>6.877545918269846</v>
+        <v>6.818984904059071</v>
       </c>
       <c r="E7" t="n">
-        <v>2.622507563052936</v>
+        <v>2.611318614045224</v>
       </c>
       <c r="F7" t="n">
-        <v>34.35435327608685</v>
+        <v>26.73057399579085</v>
       </c>
       <c r="G7" t="n">
-        <v>4.836184404845095</v>
+        <v>4.795005201242001</v>
       </c>
       <c r="H7" t="n">
-        <v>995.8439927553104</v>
+        <v>991.5341523441144</v>
       </c>
       <c r="I7" t="n">
-        <v>1046.514907972167</v>
+        <v>1042.205067560971</v>
       </c>
     </row>
     <row r="8">
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9273555972936957</v>
+        <v>0.9276048505124492</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8193750394611904</v>
+        <v>0.8088138738688363</v>
       </c>
       <c r="D8" t="n">
-        <v>6.843337195525682</v>
+        <v>6.819856737851652</v>
       </c>
       <c r="E8" t="n">
-        <v>2.615977292624246</v>
+        <v>2.611485542340155</v>
       </c>
       <c r="F8" t="n">
-        <v>30.49974398621373</v>
+        <v>27.84134951558098</v>
       </c>
       <c r="G8" t="n">
-        <v>4.812129357679868</v>
+        <v>4.795618261342422</v>
       </c>
       <c r="H8" t="n">
-        <v>993.3308553947131</v>
+        <v>991.5985865891325</v>
       </c>
       <c r="I8" t="n">
-        <v>1044.00177061157</v>
+        <v>1042.269501805989</v>
       </c>
     </row>
   </sheetData>
@@ -781,28 +781,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-135.6608189972154</v>
+        <v>0.4924310774429965</v>
       </c>
       <c r="E2" t="n">
-        <v>4.648036176251808</v>
+        <v>0.2782980333641375</v>
       </c>
       <c r="F2" t="n">
-        <v>63.63809467336314</v>
+        <v>0.236356838660521</v>
       </c>
       <c r="G2" t="n">
-        <v>7.977348849922707</v>
+        <v>0.486165443712859</v>
       </c>
       <c r="H2" t="n">
-        <v>1045.386575594097</v>
+        <v>135.7115047132339</v>
       </c>
       <c r="I2" t="n">
-        <v>171.0898239410377</v>
+        <v>0.3177204638294658</v>
       </c>
       <c r="J2" t="n">
-        <v>94.60460848604599</v>
+        <v>-0.5210139908605136</v>
       </c>
       <c r="K2" t="n">
-        <v>104.6031686147206</v>
+        <v>9.477546137814084</v>
       </c>
     </row>
     <row r="3">
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-67.00179042926707</v>
+        <v>-36.97570845998319</v>
       </c>
       <c r="E3" t="n">
-        <v>3.022400417268377</v>
+        <v>2.172508648472751</v>
       </c>
       <c r="F3" t="n">
-        <v>27.01176408866536</v>
+        <v>15.08476279147368</v>
       </c>
       <c r="G3" t="n">
-        <v>5.197284299388033</v>
+        <v>3.883910759978102</v>
       </c>
       <c r="H3" t="n">
-        <v>1101.544144759639</v>
+        <v>717.8009316507524</v>
       </c>
       <c r="I3" t="n">
-        <v>78.61754398169175</v>
+        <v>43.90409298405307</v>
       </c>
       <c r="J3" t="n">
-        <v>73.44408717148812</v>
+        <v>64.70527721539204</v>
       </c>
       <c r="K3" t="n">
-        <v>81.94068958471465</v>
+        <v>73.20187962861857</v>
       </c>
     </row>
     <row r="4">
@@ -863,28 +863,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-244.7948275413015</v>
+        <v>-244.7905352746371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7958369291484918</v>
+        <v>0.7958299601687182</v>
       </c>
       <c r="F4" t="n">
-        <v>3.226680976145115</v>
+        <v>3.226624629250719</v>
       </c>
       <c r="G4" t="n">
-        <v>1.79629646109575</v>
+        <v>1.796280776841616</v>
       </c>
       <c r="H4" t="n">
-        <v>1044.494831604717</v>
+        <v>1044.489214998129</v>
       </c>
       <c r="I4" t="n">
-        <v>151.9942498913841</v>
+        <v>151.9915956457333</v>
       </c>
       <c r="J4" t="n">
-        <v>48.60053499469146</v>
+        <v>48.60016827262537</v>
       </c>
       <c r="K4" t="n">
-        <v>61.13480424737253</v>
+        <v>61.13443752530645</v>
       </c>
     </row>
     <row r="5">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2881.943024457858</v>
+        <v>-808.8148418846989</v>
       </c>
       <c r="E5" t="n">
-        <v>2.090279675064336</v>
+        <v>1.111300426892804</v>
       </c>
       <c r="F5" t="n">
-        <v>19.38615192501742</v>
+        <v>5.44554416189442</v>
       </c>
       <c r="G5" t="n">
-        <v>4.402970806741446</v>
+        <v>2.333568975173955</v>
       </c>
       <c r="H5" t="n">
-        <v>4089.992790764136</v>
+        <v>2183.565334498173</v>
       </c>
       <c r="I5" t="n">
-        <v>1756.90642736974</v>
+        <v>493.5126669574716</v>
       </c>
       <c r="J5" t="n">
-        <v>86.25573885051415</v>
+        <v>59.59075147523228</v>
       </c>
       <c r="K5" t="n">
-        <v>98.79000810319522</v>
+        <v>72.12502072791335</v>
       </c>
     </row>
     <row r="6">
@@ -945,28 +945,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-8495.178877938575</v>
+        <v>-4571.227135941261</v>
       </c>
       <c r="E6" t="n">
-        <v>10.59475184252102</v>
+        <v>8.030249315850345</v>
       </c>
       <c r="F6" t="n">
-        <v>362.1670770350237</v>
+        <v>194.9005736759909</v>
       </c>
       <c r="G6" t="n">
-        <v>19.03068777094049</v>
+        <v>13.96067955638231</v>
       </c>
       <c r="H6" t="n">
-        <v>5541.18777043243</v>
+        <v>4210.135712560582</v>
       </c>
       <c r="I6" t="n">
-        <v>5604.741234612179</v>
+        <v>3016.197084711144</v>
       </c>
       <c r="J6" t="n">
-        <v>183.086852391248</v>
+        <v>166.3572178485635</v>
       </c>
       <c r="K6" t="n">
-        <v>198.6368947833</v>
+        <v>181.9072602406155</v>
       </c>
     </row>
     <row r="7">
@@ -986,28 +986,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-2321.132205675471</v>
+        <v>-0.7263562496424125</v>
       </c>
       <c r="E7" t="n">
-        <v>5.967373708226392</v>
+        <v>0.1656290650263679</v>
       </c>
       <c r="F7" t="n">
-        <v>87.69670681231182</v>
+        <v>0.06519687273122086</v>
       </c>
       <c r="G7" t="n">
-        <v>9.364651985648576</v>
+        <v>0.2553367829577651</v>
       </c>
       <c r="H7" t="n">
-        <v>3240.098434109121</v>
+        <v>99.99364560374359</v>
       </c>
       <c r="I7" t="n">
-        <v>1516.054712942519</v>
+        <v>1.127089371609157</v>
       </c>
       <c r="J7" t="n">
-        <v>135.847108701808</v>
+        <v>-44.25859438612324</v>
       </c>
       <c r="K7" t="n">
-        <v>150.4736186002264</v>
+        <v>-29.63208448770483</v>
       </c>
     </row>
     <row r="8">
@@ -1027,28 +1027,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.145581266823464</v>
+        <v>-0.4388671942917366</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5641514184623321</v>
+        <v>0.4548796825197845</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9991210706141616</v>
+        <v>0.670029401291673</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9995604387000125</v>
+        <v>0.8185532366875553</v>
       </c>
       <c r="H8" t="n">
-        <v>125.1235488787476</v>
+        <v>99.14360498211045</v>
       </c>
       <c r="I8" t="n">
-        <v>2.686118258953905</v>
+        <v>1.801361478383384</v>
       </c>
       <c r="J8" t="n">
-        <v>23.98505163019725</v>
+        <v>17.19262735440415</v>
       </c>
       <c r="K8" t="n">
-        <v>33.98361175887185</v>
+        <v>27.19118748307875</v>
       </c>
     </row>
     <row r="9">
@@ -1068,28 +1068,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.7965459279096596</v>
+        <v>-0.2921443169309572</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4256874217884748</v>
+        <v>0.3538021340772751</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7136264276692098</v>
+        <v>0.5132673307146752</v>
       </c>
       <c r="G9" t="n">
-        <v>0.844764125462966</v>
+        <v>0.7164267797302634</v>
       </c>
       <c r="H9" t="n">
-        <v>118.0766625761522</v>
+        <v>96.43570968453194</v>
       </c>
       <c r="I9" t="n">
-        <v>2.07700455548269</v>
+        <v>1.49386085315912</v>
       </c>
       <c r="J9" t="n">
-        <v>18.93906503831583</v>
+        <v>13.99562314441356</v>
       </c>
       <c r="K9" t="n">
-        <v>27.43566745154235</v>
+        <v>22.49222555764008</v>
       </c>
     </row>
     <row r="10">
@@ -1109,28 +1109,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.9946792703019156</v>
+        <v>-0.2229709771058641</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07868468431051752</v>
+        <v>0.06305793698076212</v>
       </c>
       <c r="F10" t="n">
-        <v>0.026185228222155</v>
+        <v>0.01605459816090725</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1618185039547548</v>
+        <v>0.1267067407871706</v>
       </c>
       <c r="H10" t="n">
-        <v>115.0591557382607</v>
+        <v>94.44315399954161</v>
       </c>
       <c r="I10" t="n">
-        <v>1.233466881692167</v>
+        <v>0.7562590236887887</v>
       </c>
       <c r="J10" t="n">
-        <v>-52.49375654611855</v>
+        <v>-62.7669595938667</v>
       </c>
       <c r="K10" t="n">
-        <v>-39.95948729343747</v>
+        <v>-50.23269034118562</v>
       </c>
     </row>
     <row r="11">
@@ -1150,28 +1150,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.301559243543827</v>
+        <v>-0.2591951100206513</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06197149379177854</v>
+        <v>0.04660688533384455</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01547667670891947</v>
+        <v>0.008467370842574972</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1244052921258556</v>
+        <v>0.09201831797297194</v>
       </c>
       <c r="H11" t="n">
-        <v>126.8091625004386</v>
+        <v>95.70208471296546</v>
       </c>
       <c r="I11" t="n">
-        <v>1.402602893518784</v>
+        <v>0.7673713851919959</v>
       </c>
       <c r="J11" t="n">
-        <v>-63.53684345184585</v>
+        <v>-76.20223976072833</v>
       </c>
       <c r="K11" t="n">
-        <v>-51.00257419916478</v>
+        <v>-63.66797050804725</v>
       </c>
     </row>
     <row r="12">
@@ -1191,28 +1191,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-66.38824420233826</v>
+        <v>-123.7373659259511</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5975317008670188</v>
+        <v>0.9070667903379744</v>
       </c>
       <c r="F12" t="n">
-        <v>2.872562334187202</v>
+        <v>5.317186450929674</v>
       </c>
       <c r="G12" t="n">
-        <v>1.694863514914166</v>
+        <v>2.30590252416048</v>
       </c>
       <c r="H12" t="n">
-        <v>257.5470818738708</v>
+        <v>411.034878893811</v>
       </c>
       <c r="I12" t="n">
-        <v>44.45453378926504</v>
+        <v>82.2864805868722</v>
       </c>
       <c r="J12" t="n">
-        <v>52.49051963245299</v>
+        <v>69.11549612292823</v>
       </c>
       <c r="K12" t="n">
-        <v>68.04056202450494</v>
+        <v>84.66553851498018</v>
       </c>
     </row>
     <row r="13">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-130.9973058900104</v>
+        <v>-0.6416549493918884</v>
       </c>
       <c r="E13" t="n">
-        <v>1.031915889669393</v>
+        <v>0.1609269320500332</v>
       </c>
       <c r="F13" t="n">
-        <v>4.984956931547353</v>
+        <v>0.061998077642579</v>
       </c>
       <c r="G13" t="n">
-        <v>2.232701711278816</v>
+        <v>0.2489941317432582</v>
       </c>
       <c r="H13" t="n">
-        <v>453.9256349189593</v>
+        <v>94.78110538456886</v>
       </c>
       <c r="I13" t="n">
-        <v>86.17732323817255</v>
+        <v>1.071790278334744</v>
       </c>
       <c r="J13" t="n">
-        <v>64.16061909417806</v>
+        <v>-45.51629750456473</v>
       </c>
       <c r="K13" t="n">
-        <v>78.78712899259648</v>
+        <v>-30.88978760614633</v>
       </c>
     </row>
     <row r="14">
@@ -1273,28 +1273,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.9139768680757299</v>
+        <v>-0.4464666394468091</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5377756937460171</v>
+        <v>0.4559645527106111</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8912711194545979</v>
+        <v>0.6735681932716434</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9440715647950625</v>
+        <v>0.8207120038549719</v>
       </c>
       <c r="H14" t="n">
-        <v>119.7048817489279</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>2.396165688081875</v>
+        <v>1.810875454248386</v>
       </c>
       <c r="J14" t="n">
-        <v>22.0431876114421</v>
+        <v>17.28217738487788</v>
       </c>
       <c r="K14" t="n">
-        <v>32.0417477401167</v>
+        <v>27.28073751355248</v>
       </c>
     </row>
     <row r="15">
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.6589340932852319</v>
+        <v>-0.322882516113336</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4629197517462072</v>
+        <v>0.3581282369858643</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6589640667340239</v>
+        <v>0.5254772001840454</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8117660172328132</v>
+        <v>0.7248980619259824</v>
       </c>
       <c r="H15" t="n">
-        <v>133.382299968785</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>1.917910149398773</v>
+        <v>1.529397589925665</v>
       </c>
       <c r="J15" t="n">
-        <v>17.74370590612093</v>
+        <v>14.34827285240432</v>
       </c>
       <c r="K15" t="n">
-        <v>26.24030831934745</v>
+        <v>22.84487526563084</v>
       </c>
     </row>
     <row r="16">
@@ -1355,28 +1355,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.989738871361058</v>
+        <v>-0.3230718182399341</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08371816731014385</v>
+        <v>0.06512401722731298</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02612037294657214</v>
+        <v>0.01736867577195525</v>
       </c>
       <c r="G16" t="n">
-        <v>0.161617984601257</v>
+        <v>0.1317902719169941</v>
       </c>
       <c r="H16" t="n">
-        <v>121.6163344797379</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>1.230411844941836</v>
+        <v>0.8181592370246979</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.54583362600216</v>
+        <v>-61.1148257008888</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.01156437332109</v>
+        <v>-48.58055644820772</v>
       </c>
     </row>
     <row r="17">
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.357721140414561</v>
+        <v>-0.3384680361618866</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09305206009593378</v>
+        <v>0.04770749428804517</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02257876468514681</v>
+        <v>0.00900043617778175</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1502623195786183</v>
+        <v>0.09487062863595745</v>
       </c>
       <c r="H17" t="n">
-        <v>170.1009576512607</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>2.046242954807942</v>
+        <v>0.8156814323460264</v>
       </c>
       <c r="J17" t="n">
-        <v>-55.60565403253922</v>
+        <v>-74.92012701106823</v>
       </c>
       <c r="K17" t="n">
-        <v>-43.07138477985814</v>
+        <v>-62.38585775838715</v>
       </c>
     </row>
     <row r="18">
@@ -1437,28 +1437,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.6655261053285841</v>
+        <v>-0.2771172166940177</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1831865187129814</v>
+        <v>0.1578769451409187</v>
       </c>
       <c r="F18" t="n">
-        <v>0.07099647146773991</v>
+        <v>0.05443974474245072</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2664516306344172</v>
+        <v>0.2333232623260071</v>
       </c>
       <c r="H18" t="n">
-        <v>86.65996171711832</v>
+        <v>76.68033144418838</v>
       </c>
       <c r="I18" t="n">
-        <v>1.098710723251986</v>
+        <v>0.8424859726558418</v>
       </c>
       <c r="J18" t="n">
-        <v>-47.41837772195791</v>
+        <v>-54.58784132990789</v>
       </c>
       <c r="K18" t="n">
-        <v>-31.86833532990596</v>
+        <v>-39.03779893785594</v>
       </c>
     </row>
     <row r="19">
@@ -1478,28 +1478,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.754514547545015</v>
+        <v>-0.433228012873508</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2149633557482317</v>
+        <v>0.1526532480932454</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1040258836667038</v>
+        <v>0.05412671015584977</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3225304383569151</v>
+        <v>0.2326514778716219</v>
       </c>
       <c r="H19" t="n">
-        <v>109.1945125832781</v>
+        <v>80.75277745604684</v>
       </c>
       <c r="I19" t="n">
-        <v>1.798344965660394</v>
+        <v>0.9357142019422946</v>
       </c>
       <c r="J19" t="n">
-        <v>-32.57788823489977</v>
+        <v>-48.91068741864277</v>
       </c>
       <c r="K19" t="n">
-        <v>-17.95137833648137</v>
+        <v>-34.28417752022436</v>
       </c>
     </row>
     <row r="20">
@@ -1519,28 +1519,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.014162533989989</v>
+        <v>-0.4464666394468091</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5480645598059254</v>
+        <v>0.4559645527106111</v>
       </c>
       <c r="F20" t="n">
-        <v>0.937924029477737</v>
+        <v>0.6735681932716434</v>
       </c>
       <c r="G20" t="n">
-        <v>0.968464779678506</v>
+        <v>0.8207120038549719</v>
       </c>
       <c r="H20" t="n">
-        <v>122.926698171629</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>2.521591161662825</v>
+        <v>1.810875454248386</v>
       </c>
       <c r="J20" t="n">
-        <v>22.91053247017297</v>
+        <v>17.28217738487788</v>
       </c>
       <c r="K20" t="n">
-        <v>32.90909259884757</v>
+        <v>27.28073751355248</v>
       </c>
     </row>
     <row r="21">
@@ -1560,28 +1560,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.754279244885846</v>
+        <v>-0.322882516113336</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4234427289129773</v>
+        <v>0.3581282369858643</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6968371980997736</v>
+        <v>0.5254772001840454</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8347677509941155</v>
+        <v>0.7248980619259824</v>
       </c>
       <c r="H21" t="n">
-        <v>121.219123583745</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>2.028139624271191</v>
+        <v>1.529397589925665</v>
       </c>
       <c r="J21" t="n">
-        <v>18.58194793973687</v>
+        <v>14.34827285240432</v>
       </c>
       <c r="K21" t="n">
-        <v>27.07855035296339</v>
+        <v>22.84487526563084</v>
       </c>
     </row>
     <row r="22">
@@ -1601,28 +1601,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.177960812994734</v>
+        <v>-0.3230718182399341</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08194365469811535</v>
+        <v>0.06512401722731298</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02859126366643656</v>
+        <v>0.01736867577195525</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1690895137684078</v>
+        <v>0.1317902719169941</v>
       </c>
       <c r="H22" t="n">
-        <v>121.9932753040303</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>1.346804256929852</v>
+        <v>0.8181592370246979</v>
       </c>
       <c r="J22" t="n">
-        <v>-50.6477355546121</v>
+        <v>-61.1148257008888</v>
       </c>
       <c r="K22" t="n">
-        <v>-38.11346630193102</v>
+        <v>-48.58055644820772</v>
       </c>
     </row>
     <row r="23">
@@ -1642,28 +1642,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-1.331121805875799</v>
+        <v>-0.3384680361618866</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06233988062054881</v>
+        <v>0.04770749428804517</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01567546812442731</v>
+        <v>0.00900043617778175</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1252017097504156</v>
+        <v>0.09487062863595745</v>
       </c>
       <c r="H23" t="n">
-        <v>128.815905725767</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>1.420618738899678</v>
+        <v>0.8156814323460264</v>
       </c>
       <c r="J23" t="n">
-        <v>-63.26882489874798</v>
+        <v>-74.92012701106823</v>
       </c>
       <c r="K23" t="n">
-        <v>-50.7345556460669</v>
+        <v>-62.38585775838715</v>
       </c>
     </row>
     <row r="24">
@@ -1683,28 +1683,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-22.05118530766255</v>
+        <v>-0.6979931889262585</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4624600577854902</v>
+        <v>0.1724917199622034</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9826041241606246</v>
+        <v>0.07238044759810999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9912639023794948</v>
+        <v>0.2690361455234407</v>
       </c>
       <c r="H24" t="n">
-        <v>224.7510844708125</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>15.20635695842241</v>
+        <v>1.120128539993109</v>
       </c>
       <c r="J24" t="n">
-        <v>23.52617802425483</v>
+        <v>-46.897115075302</v>
       </c>
       <c r="K24" t="n">
-        <v>39.07622041630678</v>
+        <v>-31.34707268325005</v>
       </c>
     </row>
     <row r="25">
@@ -1724,28 +1724,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-14.25145230356294</v>
+        <v>-0.7264614927899111</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4472665162745721</v>
+        <v>0.1656358997001203</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5759801865968517</v>
+        <v>0.06520084730141443</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7589335851027096</v>
+        <v>0.2553445658349017</v>
       </c>
       <c r="H25" t="n">
-        <v>237.2639102735054</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>9.957243643373355</v>
+        <v>1.127158081895927</v>
       </c>
       <c r="J25" t="n">
-        <v>10.20794957131914</v>
+        <v>-44.25707036783757</v>
       </c>
       <c r="K25" t="n">
-        <v>24.83445946973754</v>
+        <v>-29.63056046941917</v>
       </c>
     </row>
     <row r="26">
@@ -1765,28 +1765,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.8372084185548252</v>
+        <v>-0.4464666394468091</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5221910417409364</v>
+        <v>0.4559645527106111</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8555227762616733</v>
+        <v>0.6735681932716434</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9249447422747336</v>
+        <v>0.8207120038549719</v>
       </c>
       <c r="H26" t="n">
-        <v>116.9273633384691</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>2.300056937899238</v>
+        <v>1.810875454248386</v>
       </c>
       <c r="J26" t="n">
-        <v>21.34727643459398</v>
+        <v>17.28217738487788</v>
       </c>
       <c r="K26" t="n">
-        <v>31.34583656326858</v>
+        <v>27.28073751355248</v>
       </c>
     </row>
     <row r="27">
@@ -1806,28 +1806,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.9523972737833701</v>
+        <v>-0.322882516113336</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4461000137961366</v>
+        <v>0.3581282369858643</v>
       </c>
       <c r="F27" t="n">
-        <v>0.775533912179056</v>
+        <v>0.5254772001840454</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8806440326142317</v>
+        <v>0.7248980619259824</v>
       </c>
       <c r="H27" t="n">
-        <v>127.2149580421868</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>2.257185841320701</v>
+        <v>1.529397589925665</v>
       </c>
       <c r="J27" t="n">
-        <v>20.1869464817431</v>
+        <v>14.34827285240432</v>
       </c>
       <c r="K27" t="n">
-        <v>28.68354889496962</v>
+        <v>22.84487526563084</v>
       </c>
     </row>
     <row r="28">
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.6979775814709968</v>
+        <v>-0.3230717873081133</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07310377392080543</v>
+        <v>0.06512401633588201</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02229026548222515</v>
+        <v>0.01736867536589659</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1492992480966503</v>
+        <v>0.1317902703764454</v>
       </c>
       <c r="H28" t="n">
-        <v>110.5270951116186</v>
+        <v>99.99999832620804</v>
       </c>
       <c r="I28" t="n">
-        <v>1.049992920557713</v>
+        <v>0.8181592178971233</v>
       </c>
       <c r="J28" t="n">
-        <v>-55.87570964691768</v>
+        <v>-61.11482619184343</v>
       </c>
       <c r="K28" t="n">
-        <v>-43.34144039423661</v>
+        <v>-48.58055693916236</v>
       </c>
     </row>
     <row r="29">
@@ -1888,28 +1888,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-1.070986853502792</v>
+        <v>-0.3384678518793878</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05874747267771533</v>
+        <v>0.04770749057478482</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01392620854318441</v>
+        <v>0.009000434938586771</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1180093578627746</v>
+        <v>0.09487062210498448</v>
       </c>
       <c r="H29" t="n">
-        <v>121.3361457660009</v>
+        <v>99.99999021621751</v>
       </c>
       <c r="I29" t="n">
-        <v>1.262088804062133</v>
+        <v>0.8156813200416543</v>
       </c>
       <c r="J29" t="n">
-        <v>-65.75363685703981</v>
+        <v>-74.92012990238325</v>
       </c>
       <c r="K29" t="n">
-        <v>-53.21936760435873</v>
+        <v>-62.38586064970217</v>
       </c>
     </row>
     <row r="30">
@@ -1929,28 +1929,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8891045786084275</v>
+        <v>0.9075879595762035</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04304802945593494</v>
+        <v>0.03868869843583428</v>
       </c>
       <c r="F30" t="n">
-        <v>0.004727145131823978</v>
+        <v>0.003939253050572462</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06875423719178315</v>
+        <v>0.06276346907694365</v>
       </c>
       <c r="H30" t="n">
-        <v>31.64180795952059</v>
+        <v>24.01895981470044</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03657762800974854</v>
+        <v>0.03048108926253967</v>
       </c>
       <c r="J30" t="n">
-        <v>-120.5697132725236</v>
+        <v>-125.492632177387</v>
       </c>
       <c r="K30" t="n">
-        <v>-105.0196708804716</v>
+        <v>-109.9425897853351</v>
       </c>
     </row>
     <row r="31">
@@ -1970,28 +1970,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-2.072738444059928</v>
+        <v>-0.7264614927899111</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2221633897880338</v>
+        <v>0.1656358997001203</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1160437987901979</v>
+        <v>0.06520084730141443</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3406520200882389</v>
+        <v>0.2553445658349017</v>
       </c>
       <c r="H31" t="n">
-        <v>130.6751948211508</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>2.006104384742234</v>
+        <v>1.127158081895927</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.84468958405001</v>
+        <v>-44.25707036783757</v>
       </c>
       <c r="K31" t="n">
-        <v>-15.2181796856316</v>
+        <v>-29.63056046941917</v>
       </c>
     </row>
     <row r="32">
@@ -2011,28 +2011,28 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.104604054365191</v>
+        <v>-0.4464666394468091</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5560985260084169</v>
+        <v>0.4559645527106111</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9800394366461752</v>
+        <v>0.6735681932716434</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9899694119750242</v>
+        <v>0.8207120038549719</v>
       </c>
       <c r="H32" t="n">
-        <v>122.8129642804398</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>2.63481764392376</v>
+        <v>1.810875454248386</v>
       </c>
       <c r="J32" t="n">
-        <v>23.65723806692455</v>
+        <v>17.28217738487788</v>
       </c>
       <c r="K32" t="n">
-        <v>33.65579819559915</v>
+        <v>27.28073751355248</v>
       </c>
     </row>
     <row r="33">
@@ -2052,28 +2052,28 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.5912056862430202</v>
+        <v>-0.3101259158472696</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3992515043764227</v>
+        <v>0.3552525004253281</v>
       </c>
       <c r="F33" t="n">
-        <v>0.632060896367822</v>
+        <v>0.5204100060001099</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7950225760114125</v>
+        <v>0.7213944870874117</v>
       </c>
       <c r="H33" t="n">
-        <v>113.1969618486092</v>
+        <v>98.53343496868652</v>
       </c>
       <c r="I33" t="n">
-        <v>1.839608666660763</v>
+        <v>1.514649557908516</v>
       </c>
       <c r="J33" t="n">
-        <v>17.11845698302876</v>
+        <v>14.20292542483308</v>
       </c>
       <c r="K33" t="n">
-        <v>25.61505939625528</v>
+        <v>22.6995278380596</v>
       </c>
     </row>
     <row r="34">
@@ -2093,28 +2093,28 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-1.109775336672858</v>
+        <v>-0.3230718182399341</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08062200674009283</v>
+        <v>0.06512401722731298</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02769615622459986</v>
+        <v>0.01736867577195525</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1664216218662703</v>
+        <v>0.1317902719169941</v>
       </c>
       <c r="H34" t="n">
-        <v>120.1011321734665</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>1.304639820718155</v>
+        <v>0.8181592370246979</v>
       </c>
       <c r="J34" t="n">
-        <v>-51.31569443732042</v>
+        <v>-61.1148257008888</v>
       </c>
       <c r="K34" t="n">
-        <v>-38.78142518463934</v>
+        <v>-48.58055644820772</v>
       </c>
     </row>
     <row r="35">
@@ -2134,28 +2134,28 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-1.217348487818547</v>
+        <v>-0.2308176857126356</v>
       </c>
       <c r="E35" t="n">
-        <v>0.06085243989912711</v>
+        <v>0.04548663003589436</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01491040727856269</v>
+        <v>0.008276548806132081</v>
       </c>
       <c r="G35" t="n">
-        <v>0.122108178589981</v>
+        <v>0.09097553960341252</v>
       </c>
       <c r="H35" t="n">
-        <v>125.8908688767804</v>
+        <v>94.14841658186877</v>
       </c>
       <c r="I35" t="n">
-        <v>1.351283662881116</v>
+        <v>0.7500777797561663</v>
       </c>
       <c r="J35" t="n">
-        <v>-64.31961253037132</v>
+        <v>-76.68091337489579</v>
       </c>
       <c r="K35" t="n">
-        <v>-51.78534327769024</v>
+        <v>-64.14664412221472</v>
       </c>
     </row>
     <row r="36">
@@ -2175,28 +2175,28 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.6739854024455914</v>
+        <v>0.7955950862899669</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06960960065693771</v>
+        <v>0.05108021285376291</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01389704190122672</v>
+        <v>0.008713179323729177</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1178857154248415</v>
+        <v>0.09334441238622254</v>
       </c>
       <c r="H36" t="n">
-        <v>44.54195426352753</v>
+        <v>32.17543815466117</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1075323085971813</v>
+        <v>0.06742069963962037</v>
       </c>
       <c r="J36" t="n">
-        <v>-91.45414040757822</v>
+        <v>-104.0588004389346</v>
       </c>
       <c r="K36" t="n">
-        <v>-75.90409801552627</v>
+        <v>-88.5087580468826</v>
       </c>
     </row>
     <row r="37">
@@ -2216,28 +2216,28 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-24.17760740243209</v>
+        <v>-0.7264614927899111</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4878877467245908</v>
+        <v>0.1656358997001203</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9508473502111863</v>
+        <v>0.06520084730141443</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9751140190824795</v>
+        <v>0.2553445658349017</v>
       </c>
       <c r="H37" t="n">
-        <v>235.9385791424465</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>16.43775073175492</v>
+        <v>1.127158081895927</v>
       </c>
       <c r="J37" t="n">
-        <v>22.73995639135743</v>
+        <v>-44.25707036783757</v>
       </c>
       <c r="K37" t="n">
-        <v>37.36646628977584</v>
+        <v>-29.63056046941917</v>
       </c>
     </row>
     <row r="38">
@@ -2257,28 +2257,28 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-1.041649697936746</v>
+        <v>-0.3711986550271307</v>
       </c>
       <c r="E38" t="n">
-        <v>0.553465199862587</v>
+        <v>0.4374281678332657</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9507238264815996</v>
+        <v>0.6385185634397724</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9750506789298695</v>
+        <v>0.7990735657245661</v>
       </c>
       <c r="H38" t="n">
-        <v>125.045045030028</v>
+        <v>91.36644267497647</v>
       </c>
       <c r="I38" t="n">
-        <v>2.556003175836287</v>
+        <v>1.71664518183196</v>
       </c>
       <c r="J38" t="n">
-        <v>23.14096174785267</v>
+        <v>16.37372298291996</v>
       </c>
       <c r="K38" t="n">
-        <v>33.13952187652727</v>
+        <v>26.37228311159456</v>
       </c>
     </row>
     <row r="39">
@@ -2298,28 +2298,28 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-0.9591928390172906</v>
+        <v>-0.3172351562739102</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4500374669605516</v>
+        <v>0.3568580397716132</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7782332558844064</v>
+        <v>0.5232339481940108</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8821752977069843</v>
+        <v>0.7233491191630849</v>
       </c>
       <c r="H39" t="n">
-        <v>129.6234291959393</v>
+        <v>99.35222619386246</v>
       </c>
       <c r="I39" t="n">
-        <v>2.265042261648543</v>
+        <v>1.522868621235961</v>
       </c>
       <c r="J39" t="n">
-        <v>20.23906522533357</v>
+        <v>14.28410107121675</v>
       </c>
       <c r="K39" t="n">
-        <v>28.73566763856009</v>
+        <v>22.78070348444326</v>
       </c>
     </row>
     <row r="40">
@@ -2339,28 +2339,28 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-0.6832666134518297</v>
+        <v>-0.3230718182399341</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07279593986846049</v>
+        <v>0.06512401722731298</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02209714668829874</v>
+        <v>0.01736867577195525</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1486510904376377</v>
+        <v>0.1317902719169941</v>
       </c>
       <c r="H40" t="n">
-        <v>110.1016119007662</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>1.040895973434716</v>
+        <v>0.8181592370246979</v>
       </c>
       <c r="J40" t="n">
-        <v>-56.05844254633017</v>
+        <v>-61.1148257008888</v>
       </c>
       <c r="K40" t="n">
-        <v>-43.52417329364909</v>
+        <v>-48.58055644820772</v>
       </c>
     </row>
     <row r="41">
@@ -2380,28 +2380,28 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-0.9638047719487719</v>
+        <v>-0.3384680361618866</v>
       </c>
       <c r="E41" t="n">
-        <v>0.05738794800161832</v>
+        <v>0.04770749428804517</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01320547001348815</v>
+        <v>0.00900043617778175</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1149150556432365</v>
+        <v>0.09487062863595745</v>
       </c>
       <c r="H41" t="n">
-        <v>119.0694723479618</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
-        <v>1.196770521188147</v>
+        <v>0.8156814323460264</v>
       </c>
       <c r="J41" t="n">
-        <v>-66.86960694559582</v>
+        <v>-74.92012701106823</v>
       </c>
       <c r="K41" t="n">
-        <v>-54.33533769291474</v>
+        <v>-62.38585775838715</v>
       </c>
     </row>
     <row r="42">
@@ -2421,28 +2421,28 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-0.6979927978201819</v>
+        <v>-0.6979931889262585</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1724917029835674</v>
+        <v>0.1724917199622034</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07238043092641008</v>
+        <v>0.07238044759810999</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2690361145393125</v>
+        <v>0.2690361455234407</v>
       </c>
       <c r="H42" t="n">
-        <v>99.99999208534001</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>1.120128281989083</v>
+        <v>1.120128539993109</v>
       </c>
       <c r="J42" t="n">
-        <v>-46.89712129432887</v>
+        <v>-46.897115075302</v>
       </c>
       <c r="K42" t="n">
-        <v>-31.34707890227692</v>
+        <v>-31.34707268325005</v>
       </c>
     </row>
     <row r="43">
@@ -2462,28 +2462,28 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-2.625719114493297</v>
+        <v>0.05872831010773494</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1765899492263499</v>
+        <v>0.1130972116177432</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1369274434032592</v>
+        <v>0.03554768639677854</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3700370838216884</v>
+        <v>0.1885409409035039</v>
       </c>
       <c r="H43" t="n">
-        <v>87.79599223267365</v>
+        <v>66.62614372487097</v>
       </c>
       <c r="I43" t="n">
-        <v>2.367129889460541</v>
+        <v>0.3072648874454245</v>
       </c>
       <c r="J43" t="n">
-        <v>-25.70760259105539</v>
+        <v>-59.42200512775233</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.08109269263699</v>
+        <v>-44.79549522933392</v>
       </c>
     </row>
   </sheetData>

--- a/results/modelling/metrics_summary_all_models.xlsx
+++ b/results/modelling/metrics_summary_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,96 +483,96 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8085139113098889</v>
+        <v>0.7033728793076519</v>
       </c>
       <c r="C2" t="n">
-        <v>1.355803109305723</v>
+        <v>1.563830424306519</v>
       </c>
       <c r="D2" t="n">
-        <v>18.03860757802122</v>
+        <v>27.94323213644467</v>
       </c>
       <c r="E2" t="n">
-        <v>4.24718819668039</v>
+        <v>5.286135841656424</v>
       </c>
       <c r="F2" t="n">
-        <v>247.2439123848417</v>
+        <v>339.9181579307157</v>
       </c>
       <c r="G2" t="n">
-        <v>12.68447113122189</v>
+        <v>19.65525063171897</v>
       </c>
       <c r="H2" t="n">
-        <v>1481.827220506472</v>
+        <v>1702.40821434952</v>
       </c>
       <c r="I2" t="n">
-        <v>1532.498135723328</v>
+        <v>1753.079129566376</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9246009932515711</v>
+        <v>0.9275759949690897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8509043639312235</v>
+        <v>0.812082653538304</v>
       </c>
       <c r="D3" t="n">
-        <v>7.102829786808017</v>
+        <v>6.822575023167695</v>
       </c>
       <c r="E3" t="n">
-        <v>2.665113466028795</v>
+        <v>2.612005938578183</v>
       </c>
       <c r="F3" t="n">
-        <v>40.58835968631103</v>
+        <v>29.39806881349626</v>
       </c>
       <c r="G3" t="n">
-        <v>4.99460055279014</v>
+        <v>4.803529717726659</v>
       </c>
       <c r="H3" t="n">
-        <v>1012.08860614715</v>
+        <v>991.799432866602</v>
       </c>
       <c r="I3" t="n">
-        <v>1062.759521364006</v>
+        <v>1042.470348083458</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9275920116120691</v>
+        <v>0.9275764768471575</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8106560840382336</v>
+        <v>0.8120164552850134</v>
       </c>
       <c r="D4" t="n">
-        <v>6.821066203705157</v>
+        <v>6.822529628698443</v>
       </c>
       <c r="E4" t="n">
-        <v>2.611717098712102</v>
+        <v>2.611997248983705</v>
       </c>
       <c r="F4" t="n">
-        <v>27.74789787998624</v>
+        <v>29.35995718395916</v>
       </c>
       <c r="G4" t="n">
-        <v>4.796468739109989</v>
+        <v>4.803497797034763</v>
       </c>
       <c r="H4" t="n">
-        <v>991.6879604232016</v>
+        <v>991.7960794569967</v>
       </c>
       <c r="I4" t="n">
-        <v>1042.358875640058</v>
+        <v>1042.466994673853</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -591,7 +591,7 @@
         <v>29.39809040691511</v>
       </c>
       <c r="G5" t="n">
-        <v>4.797530841899115</v>
+        <v>4.803530841899115</v>
       </c>
       <c r="H5" t="n">
         <v>991.7995509654747</v>
@@ -603,94 +603,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9276148990918043</v>
+        <v>0.9275917518732469</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8049149790896489</v>
+        <v>0.8094453941533872</v>
       </c>
       <c r="D6" t="n">
-        <v>6.818910129244501</v>
+        <v>6.821090671940501</v>
       </c>
       <c r="E6" t="n">
-        <v>2.611304296562257</v>
+        <v>2.61172178302753</v>
       </c>
       <c r="F6" t="n">
-        <v>26.55153827105423</v>
+        <v>28.03645633445525</v>
       </c>
       <c r="G6" t="n">
-        <v>4.794952620743609</v>
+        <v>4.802485944796377</v>
       </c>
       <c r="H6" t="n">
-        <v>991.5286256104871</v>
+        <v>991.6897683470844</v>
       </c>
       <c r="I6" t="n">
-        <v>1042.199540827344</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>induction_qP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.92761410533116</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.8054006869949294</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6.818984904059071</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.611318614045224</v>
-      </c>
-      <c r="F7" t="n">
-        <v>26.73057399579085</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.795005201242001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>991.5341523441144</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1042.205067560971</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9276048505124492</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.8088138738688363</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.819856737851652</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.611485542340155</v>
-      </c>
-      <c r="F8" t="n">
-        <v>27.84134951558098</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4.795618261342422</v>
-      </c>
-      <c r="H8" t="n">
-        <v>991.5985865891325</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1042.269501805989</v>
+        <v>1042.360683563941</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,28 +719,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4924310774429965</v>
+        <v>-0.01583300212114458</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2782980333641375</v>
+        <v>0.4134203562565844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.236356838660521</v>
+        <v>0.4730373872750558</v>
       </c>
       <c r="G2" t="n">
-        <v>0.486165443712859</v>
+        <v>0.6877771348882251</v>
       </c>
       <c r="H2" t="n">
-        <v>135.7115047132339</v>
+        <v>274.8962485921093</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3177204638294658</v>
+        <v>1.283752143457765</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5210139908605136</v>
+        <v>11.27412553726504</v>
       </c>
       <c r="K2" t="n">
-        <v>9.477546137814084</v>
+        <v>21.27268566593964</v>
       </c>
     </row>
     <row r="3">
@@ -822,28 +760,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-36.97570845998319</v>
+        <v>-67.00240132732108</v>
       </c>
       <c r="E3" t="n">
-        <v>2.172508648472751</v>
+        <v>3.022412770126482</v>
       </c>
       <c r="F3" t="n">
-        <v>15.08476279147368</v>
+        <v>27.0120067504249</v>
       </c>
       <c r="G3" t="n">
-        <v>3.883910759978102</v>
+        <v>5.197307644389054</v>
       </c>
       <c r="H3" t="n">
-        <v>717.8009316507524</v>
+        <v>1101.547071144086</v>
       </c>
       <c r="I3" t="n">
-        <v>43.90409298405307</v>
+        <v>78.63025024698752</v>
       </c>
       <c r="J3" t="n">
-        <v>64.70527721539204</v>
+        <v>73.44422192425849</v>
       </c>
       <c r="K3" t="n">
-        <v>73.20187962861857</v>
+        <v>81.940824337485</v>
       </c>
     </row>
     <row r="4">
@@ -863,28 +801,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-244.7905352746371</v>
+        <v>-244.7949350469203</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7958299601687182</v>
+        <v>0.795836302837803</v>
       </c>
       <c r="F4" t="n">
-        <v>3.226624629250719</v>
+        <v>3.226682387429227</v>
       </c>
       <c r="G4" t="n">
-        <v>1.796280776841616</v>
+        <v>1.796296853927331</v>
       </c>
       <c r="H4" t="n">
-        <v>1044.489214998129</v>
+        <v>1044.493148356004</v>
       </c>
       <c r="I4" t="n">
-        <v>151.9915956457333</v>
+        <v>152.0063163705531</v>
       </c>
       <c r="J4" t="n">
-        <v>48.60016827262537</v>
+        <v>48.60054417965895</v>
       </c>
       <c r="K4" t="n">
-        <v>61.13443752530645</v>
+        <v>61.13481343234002</v>
       </c>
     </row>
     <row r="5">
@@ -904,28 +842,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-808.8148418846989</v>
+        <v>-2881.917923734907</v>
       </c>
       <c r="E5" t="n">
-        <v>1.111300426892804</v>
+        <v>2.090270615345486</v>
       </c>
       <c r="F5" t="n">
-        <v>5.44554416189442</v>
+        <v>19.3859831369337</v>
       </c>
       <c r="G5" t="n">
-        <v>2.333568975173955</v>
+        <v>4.402951639177258</v>
       </c>
       <c r="H5" t="n">
-        <v>2183.565334498173</v>
+        <v>4089.976425866724</v>
       </c>
       <c r="I5" t="n">
-        <v>493.5126669574716</v>
+        <v>1756.903130632651</v>
       </c>
       <c r="J5" t="n">
-        <v>59.59075147523228</v>
+        <v>86.25555601045376</v>
       </c>
       <c r="K5" t="n">
-        <v>72.12502072791335</v>
+        <v>98.78982526313484</v>
       </c>
     </row>
     <row r="6">
@@ -945,28 +883,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-4571.227135941261</v>
+        <v>-8495.224759197712</v>
       </c>
       <c r="E6" t="n">
-        <v>8.030249315850345</v>
+        <v>10.59477149757934</v>
       </c>
       <c r="F6" t="n">
-        <v>194.9005736759909</v>
+        <v>362.1690328179412</v>
       </c>
       <c r="G6" t="n">
-        <v>13.96067955638231</v>
+        <v>19.03073915584839</v>
       </c>
       <c r="H6" t="n">
-        <v>4210.135712560582</v>
+        <v>5541.194827780638</v>
       </c>
       <c r="I6" t="n">
-        <v>3016.197084711144</v>
+        <v>5604.783501463746</v>
       </c>
       <c r="J6" t="n">
-        <v>166.3572178485635</v>
+        <v>183.0869981968707</v>
       </c>
       <c r="K6" t="n">
-        <v>181.9072602406155</v>
+        <v>198.6370405889227</v>
       </c>
     </row>
     <row r="7">
@@ -986,34 +924,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.7263562496424125</v>
+        <v>-0.7260602469572479</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1656290650263679</v>
+        <v>0.1656098405553068</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06519687273122086</v>
+        <v>0.06518569401338857</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2553367829577651</v>
+        <v>0.255314891875481</v>
       </c>
       <c r="H7" t="n">
-        <v>99.99364560374359</v>
+        <v>99.97577205024716</v>
       </c>
       <c r="I7" t="n">
-        <v>1.127089371609157</v>
+        <v>1.138896119793093</v>
       </c>
       <c r="J7" t="n">
-        <v>-44.25859438612324</v>
+        <v>-44.26288127743808</v>
       </c>
       <c r="K7" t="n">
-        <v>-29.63208448770483</v>
+        <v>-29.63637137901968</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1027,34 +965,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.4388671942917366</v>
+        <v>-0.4463648571956385</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4548796825197845</v>
+        <v>0.4559543323382335</v>
       </c>
       <c r="F8" t="n">
-        <v>0.670029401291673</v>
+        <v>0.6735207968885133</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8185532366875553</v>
+        <v>0.820683128185607</v>
       </c>
       <c r="H8" t="n">
-        <v>99.14360498211045</v>
+        <v>99.99906338545736</v>
       </c>
       <c r="I8" t="n">
-        <v>1.801361478383384</v>
+        <v>1.822748029961302</v>
       </c>
       <c r="J8" t="n">
-        <v>17.19262735440415</v>
+        <v>17.28098111867805</v>
       </c>
       <c r="K8" t="n">
-        <v>27.19118748307875</v>
+        <v>27.27954124735265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1068,34 +1006,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.2921443169309572</v>
+        <v>-0.322882516113336</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3538021340772751</v>
+        <v>0.3581282369858643</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5132673307146752</v>
+        <v>0.5254772001840454</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7164267797302634</v>
+        <v>0.7248980619259824</v>
       </c>
       <c r="H9" t="n">
-        <v>96.43570968453194</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>1.49386085315912</v>
+        <v>1.541397589925665</v>
       </c>
       <c r="J9" t="n">
-        <v>13.99562314441356</v>
+        <v>14.34827285240432</v>
       </c>
       <c r="K9" t="n">
-        <v>22.49222555764008</v>
+        <v>22.84487526563084</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1109,34 +1047,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2229709771058641</v>
+        <v>-0.3230718182399341</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06305793698076212</v>
+        <v>0.06512401722731298</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01605459816090725</v>
+        <v>0.01736867577195525</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1267067407871706</v>
+        <v>0.1317902719169941</v>
       </c>
       <c r="H10" t="n">
-        <v>94.44315399954161</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7562590236887887</v>
+        <v>0.830159237024698</v>
       </c>
       <c r="J10" t="n">
-        <v>-62.7669595938667</v>
+        <v>-61.1148257008888</v>
       </c>
       <c r="K10" t="n">
-        <v>-50.23269034118562</v>
+        <v>-48.58055644820772</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1150,34 +1088,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.2591951100206513</v>
+        <v>-0.3384680361618866</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04660688533384455</v>
+        <v>0.04770749428804517</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008467370842574972</v>
+        <v>0.00900043617778175</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09201831797297194</v>
+        <v>0.09487062863595745</v>
       </c>
       <c r="H11" t="n">
-        <v>95.70208471296546</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7673713851919959</v>
+        <v>0.8276814323460264</v>
       </c>
       <c r="J11" t="n">
-        <v>-76.20223976072833</v>
+        <v>-74.92012701106823</v>
       </c>
       <c r="K11" t="n">
-        <v>-63.66797050804725</v>
+        <v>-62.38585775838715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1191,34 +1129,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-123.7373659259511</v>
+        <v>-0.6979931889262585</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9070667903379744</v>
+        <v>0.1724917199622034</v>
       </c>
       <c r="F12" t="n">
-        <v>5.317186450929674</v>
+        <v>0.07238044759810999</v>
       </c>
       <c r="G12" t="n">
-        <v>2.30590252416048</v>
+        <v>0.2690361455234407</v>
       </c>
       <c r="H12" t="n">
-        <v>411.034878893811</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>82.2864805868722</v>
+        <v>1.132128539993109</v>
       </c>
       <c r="J12" t="n">
-        <v>69.11549612292823</v>
+        <v>-46.897115075302</v>
       </c>
       <c r="K12" t="n">
-        <v>84.66553851498018</v>
+        <v>-31.34707268325005</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1232,34 +1170,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.6416549493918884</v>
+        <v>-0.7264614927899111</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1609269320500332</v>
+        <v>0.1656358997001203</v>
       </c>
       <c r="F13" t="n">
-        <v>0.061998077642579</v>
+        <v>0.06520084730141443</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2489941317432582</v>
+        <v>0.2553445658349017</v>
       </c>
       <c r="H13" t="n">
-        <v>94.78110538456886</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>1.071790278334744</v>
+        <v>1.139158081895927</v>
       </c>
       <c r="J13" t="n">
-        <v>-45.51629750456473</v>
+        <v>-44.25707036783757</v>
       </c>
       <c r="K13" t="n">
-        <v>-30.88978760614633</v>
+        <v>-29.63056046941917</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1288,7 +1226,7 @@
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>1.810875454248386</v>
+        <v>1.822875454248386</v>
       </c>
       <c r="J14" t="n">
         <v>17.28217738487788</v>
@@ -1300,7 +1238,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1329,7 +1267,7 @@
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>1.529397589925665</v>
+        <v>1.541397589925665</v>
       </c>
       <c r="J15" t="n">
         <v>14.34827285240432</v>
@@ -1341,7 +1279,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1370,7 +1308,7 @@
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8181592370246979</v>
+        <v>0.830159237024698</v>
       </c>
       <c r="J16" t="n">
         <v>-61.1148257008888</v>
@@ -1382,7 +1320,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1411,7 +1349,7 @@
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8156814323460264</v>
+        <v>0.8276814323460264</v>
       </c>
       <c r="J17" t="n">
         <v>-74.92012701106823</v>
@@ -1423,7 +1361,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1437,34 +1375,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.2771172166940177</v>
+        <v>-0.6774145733282249</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1578769451409187</v>
+        <v>0.1712495839532497</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05443974474245072</v>
+        <v>0.07150324183683304</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2333232623260071</v>
+        <v>0.2674009009648865</v>
       </c>
       <c r="H18" t="n">
-        <v>76.68033144418838</v>
+        <v>98.98213627887546</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8424859726558418</v>
+        <v>1.118553282568501</v>
       </c>
       <c r="J18" t="n">
-        <v>-54.58784132990789</v>
+        <v>-47.22633722823775</v>
       </c>
       <c r="K18" t="n">
-        <v>-39.03779893785594</v>
+        <v>-31.6762948361858</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1478,34 +1416,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.433228012873508</v>
+        <v>-0.7264614927899111</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1526532480932454</v>
+        <v>0.1656358997001203</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05412671015584977</v>
+        <v>0.06520084730141443</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2326514778716219</v>
+        <v>0.2553445658349017</v>
       </c>
       <c r="H19" t="n">
-        <v>80.75277745604684</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9357142019422946</v>
+        <v>1.139158081895927</v>
       </c>
       <c r="J19" t="n">
-        <v>-48.91068741864277</v>
+        <v>-44.25707036783757</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.28417752022436</v>
+        <v>-29.63056046941917</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1534,7 +1472,7 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>1.810875454248386</v>
+        <v>1.822875454248386</v>
       </c>
       <c r="J20" t="n">
         <v>17.28217738487788</v>
@@ -1546,7 +1484,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1575,7 +1513,7 @@
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>1.529397589925665</v>
+        <v>1.541397589925665</v>
       </c>
       <c r="J21" t="n">
         <v>14.34827285240432</v>
@@ -1587,7 +1525,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1616,7 +1554,7 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8181592370246979</v>
+        <v>0.830159237024698</v>
       </c>
       <c r="J22" t="n">
         <v>-61.1148257008888</v>
@@ -1628,7 +1566,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1657,7 +1595,7 @@
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8156814323460264</v>
+        <v>0.8276814323460264</v>
       </c>
       <c r="J23" t="n">
         <v>-74.92012701106823</v>
@@ -1669,7 +1607,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1698,7 +1636,7 @@
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>1.120128539993109</v>
+        <v>1.132128539993109</v>
       </c>
       <c r="J24" t="n">
         <v>-46.897115075302</v>
@@ -1710,7 +1648,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1739,7 +1677,7 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>1.127158081895927</v>
+        <v>1.139158081895927</v>
       </c>
       <c r="J25" t="n">
         <v>-44.25707036783757</v>
@@ -1751,7 +1689,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1780,7 +1718,7 @@
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>1.810875454248386</v>
+        <v>1.822875454248386</v>
       </c>
       <c r="J26" t="n">
         <v>17.28217738487788</v>
@@ -1792,7 +1730,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1821,7 +1759,7 @@
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>1.529397589925665</v>
+        <v>1.541397589925665</v>
       </c>
       <c r="J27" t="n">
         <v>14.34827285240432</v>
@@ -1833,7 +1771,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1847,34 +1785,34 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.3230717873081133</v>
+        <v>-0.3230718182399341</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06512401633588201</v>
+        <v>0.06512401722731298</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01736867536589659</v>
+        <v>0.01736867577195525</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1317902703764454</v>
+        <v>0.1317902719169941</v>
       </c>
       <c r="H28" t="n">
-        <v>99.99999832620804</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8181592178971233</v>
+        <v>0.830159237024698</v>
       </c>
       <c r="J28" t="n">
-        <v>-61.11482619184343</v>
+        <v>-61.1148257008888</v>
       </c>
       <c r="K28" t="n">
-        <v>-48.58055693916236</v>
+        <v>-48.58055644820772</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1888,34 +1826,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.3384678518793878</v>
+        <v>-0.3384680361618866</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04770749057478482</v>
+        <v>0.04770749428804517</v>
       </c>
       <c r="F29" t="n">
-        <v>0.009000434938586771</v>
+        <v>0.00900043617778175</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09487062210498448</v>
+        <v>0.09487062863595745</v>
       </c>
       <c r="H29" t="n">
-        <v>99.99999021621751</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8156813200416543</v>
+        <v>0.8276814323460264</v>
       </c>
       <c r="J29" t="n">
-        <v>-74.92012990238325</v>
+        <v>-74.92012701106823</v>
       </c>
       <c r="K29" t="n">
-        <v>-62.38586064970217</v>
+        <v>-62.38585775838715</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1929,34 +1867,34 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.9075879595762035</v>
+        <v>-0.6979931889262585</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03868869843583428</v>
+        <v>0.1724917199622034</v>
       </c>
       <c r="F30" t="n">
-        <v>0.003939253050572462</v>
+        <v>0.07238044759810999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06276346907694365</v>
+        <v>0.2690361455234407</v>
       </c>
       <c r="H30" t="n">
-        <v>24.01895981470044</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03048108926253967</v>
+        <v>1.132128539993109</v>
       </c>
       <c r="J30" t="n">
-        <v>-125.492632177387</v>
+        <v>-46.897115075302</v>
       </c>
       <c r="K30" t="n">
-        <v>-109.9425897853351</v>
+        <v>-31.34707268325005</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1970,520 +1908,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.7264614927899111</v>
+        <v>0.06676708920238184</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1656358997001203</v>
+        <v>0.1124618005351112</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06520084730141443</v>
+        <v>0.03524409711290005</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2553445658349017</v>
+        <v>0.1877341128109115</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>66.25092691877812</v>
       </c>
       <c r="I31" t="n">
-        <v>1.127158081895927</v>
+        <v>0.3106407412183155</v>
       </c>
       <c r="J31" t="n">
-        <v>-44.25707036783757</v>
+        <v>-59.63643053841375</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.63056046941917</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>induction_qP</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>raw\BR02.xls</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>-0.4464666394468091</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.4559645527106111</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.6735681932716434</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.8207120038549719</v>
-      </c>
-      <c r="H32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.810875454248386</v>
-      </c>
-      <c r="J32" t="n">
-        <v>17.28217738487788</v>
-      </c>
-      <c r="K32" t="n">
-        <v>27.28073751355248</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>induction_qP</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>raw\BR03.xls</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>-0.3101259158472696</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.3552525004253281</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.5204100060001099</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.7213944870874117</v>
-      </c>
-      <c r="H33" t="n">
-        <v>98.53343496868652</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.514649557908516</v>
-      </c>
-      <c r="J33" t="n">
-        <v>14.20292542483308</v>
-      </c>
-      <c r="K33" t="n">
-        <v>22.6995278380596</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>induction_qP</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>raw\BR04.xls</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>-0.3230718182399341</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.06512401722731298</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.01736867577195525</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.1317902719169941</v>
-      </c>
-      <c r="H34" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.8181592370246979</v>
-      </c>
-      <c r="J34" t="n">
-        <v>-61.1148257008888</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-48.58055644820772</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>induction_qP</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>raw\BR05.xls</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>-0.2308176857126356</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.04548663003589436</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.008276548806132081</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.09097553960341252</v>
-      </c>
-      <c r="H35" t="n">
-        <v>94.14841658186877</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.7500777797561663</v>
-      </c>
-      <c r="J35" t="n">
-        <v>-76.68091337489579</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-64.14664412221472</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>induction_qP</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>raw\BR07.xls</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0.7955950862899669</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.05108021285376291</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.008713179323729177</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.09334441238622254</v>
-      </c>
-      <c r="H36" t="n">
-        <v>32.17543815466117</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.06742069963962037</v>
-      </c>
-      <c r="J36" t="n">
-        <v>-104.0588004389346</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-88.5087580468826</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>induction_qP</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>raw\BR08.xls</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.7264614927899111</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.1656358997001203</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.06520084730141443</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.2553445658349017</v>
-      </c>
-      <c r="H37" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.127158081895927</v>
-      </c>
-      <c r="J37" t="n">
-        <v>-44.25707036783757</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-29.63056046941917</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>raw\BR02.xls</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>-0.3711986550271307</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.4374281678332657</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.6385185634397724</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.7990735657245661</v>
-      </c>
-      <c r="H38" t="n">
-        <v>91.36644267497647</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1.71664518183196</v>
-      </c>
-      <c r="J38" t="n">
-        <v>16.37372298291996</v>
-      </c>
-      <c r="K38" t="n">
-        <v>26.37228311159456</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>raw\BR03.xls</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.3172351562739102</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.3568580397716132</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.5232339481940108</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.7233491191630849</v>
-      </c>
-      <c r="H39" t="n">
-        <v>99.35222619386246</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1.522868621235961</v>
-      </c>
-      <c r="J39" t="n">
-        <v>14.28410107121675</v>
-      </c>
-      <c r="K39" t="n">
-        <v>22.78070348444326</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>raw\BR04.xls</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.3230718182399341</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.06512401722731298</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.01736867577195525</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.1317902719169941</v>
-      </c>
-      <c r="H40" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.8181592370246979</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-61.1148257008888</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-48.58055644820772</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>raw\BR05.xls</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.3384680361618866</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.04770749428804517</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.00900043617778175</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.09487062863595745</v>
-      </c>
-      <c r="H41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.8156814323460264</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-74.92012701106823</v>
-      </c>
-      <c r="K41" t="n">
-        <v>-62.38585775838715</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>raw\BR07.xls</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>-0.6979931889262585</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.1724917199622034</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.07238044759810999</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.2690361455234407</v>
-      </c>
-      <c r="H42" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1.120128539993109</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-46.897115075302</v>
-      </c>
-      <c r="K42" t="n">
-        <v>-31.34707268325005</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>raw\BR08.xls</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.05872831010773494</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.1130972116177432</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.03554768639677854</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.1885409409035039</v>
-      </c>
-      <c r="H43" t="n">
-        <v>66.62614372487097</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.3072648874454245</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-59.42200512775233</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-44.79549522933392</v>
+        <v>-45.00992063999534</v>
       </c>
     </row>
   </sheetData>

--- a/results/modelling/metrics_summary_all_models.xlsx
+++ b/results/modelling/metrics_summary_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,152 +483,214 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7033728793076519</v>
+        <v>0.6858376492188204</v>
       </c>
       <c r="C2" t="n">
-        <v>1.563830424306519</v>
+        <v>1.674785349640658</v>
       </c>
       <c r="D2" t="n">
-        <v>27.94323213644467</v>
+        <v>29.59510740595649</v>
       </c>
       <c r="E2" t="n">
-        <v>5.286135841656424</v>
+        <v>5.440138546577329</v>
       </c>
       <c r="F2" t="n">
-        <v>339.9181579307157</v>
+        <v>426.1993360172079</v>
       </c>
       <c r="G2" t="n">
-        <v>19.65525063171897</v>
+        <v>20.8168238894039</v>
       </c>
       <c r="H2" t="n">
-        <v>1702.40821434952</v>
+        <v>1731.354964893692</v>
       </c>
       <c r="I2" t="n">
-        <v>1753.079129566376</v>
+        <v>1782.025880110548</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9275759949690897</v>
+        <v>0.9276767947032194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.812082653538304</v>
+        <v>0.8143521485957379</v>
       </c>
       <c r="D3" t="n">
-        <v>6.822575023167695</v>
+        <v>6.813079362880449</v>
       </c>
       <c r="E3" t="n">
-        <v>2.612005938578183</v>
+        <v>2.610187610667182</v>
       </c>
       <c r="F3" t="n">
-        <v>29.39806881349626</v>
+        <v>33.38578452227281</v>
       </c>
       <c r="G3" t="n">
-        <v>4.803529717726659</v>
+        <v>4.796852515605349</v>
       </c>
       <c r="H3" t="n">
-        <v>991.799432866602</v>
+        <v>991.0974770347943</v>
       </c>
       <c r="I3" t="n">
-        <v>1042.470348083458</v>
+        <v>1041.768392251651</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9275764768471575</v>
+        <v>0.9279610434322036</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8120164552850134</v>
+        <v>0.789528458579741</v>
       </c>
       <c r="D4" t="n">
-        <v>6.822529628698443</v>
+        <v>6.786302215194306</v>
       </c>
       <c r="E4" t="n">
-        <v>2.611997248983705</v>
+        <v>2.605053207747263</v>
       </c>
       <c r="F4" t="n">
-        <v>29.35995718395916</v>
+        <v>23.19477703264317</v>
       </c>
       <c r="G4" t="n">
-        <v>4.803497797034763</v>
+        <v>4.778023237606353</v>
       </c>
       <c r="H4" t="n">
-        <v>991.7960794569967</v>
+        <v>989.1127250374955</v>
       </c>
       <c r="I4" t="n">
-        <v>1042.466994673853</v>
+        <v>1039.783640254352</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.927575977998466</v>
+        <v>0.9274113015424745</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8120829982730866</v>
+        <v>0.8134729904131718</v>
       </c>
       <c r="D5" t="n">
-        <v>6.822576621855221</v>
+        <v>6.838089675504649</v>
       </c>
       <c r="E5" t="n">
-        <v>2.612006244604944</v>
+        <v>2.614974125207485</v>
       </c>
       <c r="F5" t="n">
-        <v>29.39809040691511</v>
+        <v>28.4637293293266</v>
       </c>
       <c r="G5" t="n">
-        <v>4.803530841899115</v>
+        <v>4.814439382390512</v>
       </c>
       <c r="H5" t="n">
-        <v>991.7995509654747</v>
+        <v>992.944236331479</v>
       </c>
       <c r="I5" t="n">
-        <v>1042.470466182331</v>
+        <v>1043.615151548335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>global_ind_rP</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9279192672449763</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7903234480988496</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.79023766686421</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.605808447845737</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23.44910777600707</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.780790586631454</v>
+      </c>
+      <c r="H6" t="n">
+        <v>989.4049154946247</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1040.075830711481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>induction_qP</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9277146686156172</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8031048113699013</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.809511518094115</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.609504075125026</v>
+      </c>
+      <c r="F7" t="n">
+        <v>26.46133930617218</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.794343662081195</v>
+      </c>
+      <c r="H7" t="n">
+        <v>990.8334752998616</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1041.504390516718</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>induction_rP</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.9275917518732469</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.8094453941533872</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.821090671940501</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.61172178302753</v>
-      </c>
-      <c r="F6" t="n">
-        <v>28.03645633445525</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.802485944796377</v>
-      </c>
-      <c r="H6" t="n">
-        <v>991.6897683470844</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1042.360683563941</v>
+      <c r="B8" t="n">
+        <v>0.9272771322676369</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8021099342463233</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.850728854227143</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.617389702399538</v>
+      </c>
+      <c r="F8" t="n">
+        <v>23.54852011162094</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.823327058278709</v>
+      </c>
+      <c r="H8" t="n">
+        <v>993.874944540158</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1044.545859757015</v>
       </c>
     </row>
   </sheetData>
@@ -642,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,45 +720,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>variable</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>MAE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>MAE</t>
+          <t>MSE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>MSE</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>MAPE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>MAPE</t>
+          <t>SCORE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SCORE</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>AIC</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
@@ -710,37 +767,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>raw\BR02.xls</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.02647133941943491</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01583300212114458</v>
+        <v>0.4145297220830514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4134203562565844</v>
+        <v>0.4779912835060565</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4730373872750558</v>
+        <v>0.6913691369348623</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6877771348882251</v>
+        <v>275.8946235261489</v>
       </c>
       <c r="H2" t="n">
-        <v>274.8962485921093</v>
+        <v>1.29707060056014</v>
       </c>
       <c r="I2" t="n">
-        <v>1.283752143457765</v>
+        <v>11.45123270600128</v>
       </c>
       <c r="J2" t="n">
-        <v>11.27412553726504</v>
-      </c>
-      <c r="K2" t="n">
-        <v>21.27268566593964</v>
+        <v>21.44979283467588</v>
       </c>
     </row>
     <row r="3">
@@ -751,37 +803,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>raw\BR03.xls</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-67.00228262484909</v>
       </c>
       <c r="D3" t="n">
-        <v>-67.00240132732108</v>
+        <v>3.022410473726135</v>
       </c>
       <c r="E3" t="n">
-        <v>3.022412770126482</v>
+        <v>27.01195959926681</v>
       </c>
       <c r="F3" t="n">
-        <v>27.0120067504249</v>
+        <v>5.197303108273252</v>
       </c>
       <c r="G3" t="n">
-        <v>5.197307644389054</v>
+        <v>1101.546535684024</v>
       </c>
       <c r="H3" t="n">
-        <v>1101.547071144086</v>
+        <v>78.63011301388299</v>
       </c>
       <c r="I3" t="n">
-        <v>78.63025024698752</v>
+        <v>73.44419574079143</v>
       </c>
       <c r="J3" t="n">
-        <v>73.44422192425849</v>
-      </c>
-      <c r="K3" t="n">
-        <v>81.940824337485</v>
+        <v>81.94079815401795</v>
       </c>
     </row>
     <row r="4">
@@ -792,37 +839,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw\BR04.xls</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-3264.48404192818</v>
       </c>
       <c r="D4" t="n">
-        <v>-244.7949350469203</v>
+        <v>3.457857740383385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.795836302837803</v>
+        <v>42.86776634559004</v>
       </c>
       <c r="F4" t="n">
-        <v>3.226682387429227</v>
+        <v>6.547348039136918</v>
       </c>
       <c r="G4" t="n">
-        <v>1.796296853927331</v>
+        <v>6033.09380528493</v>
       </c>
       <c r="H4" t="n">
-        <v>1044.493148356004</v>
+        <v>2019.317298040734</v>
       </c>
       <c r="I4" t="n">
-        <v>152.0063163705531</v>
+        <v>102.9205237018899</v>
       </c>
       <c r="J4" t="n">
-        <v>48.60054417965895</v>
-      </c>
-      <c r="K4" t="n">
-        <v>61.13481343234002</v>
+        <v>115.454792954571</v>
       </c>
     </row>
     <row r="5">
@@ -833,37 +875,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>raw\BR05.xls</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-2881.916274196644</v>
       </c>
       <c r="D5" t="n">
-        <v>-2881.917923734907</v>
+        <v>2.090269996544669</v>
       </c>
       <c r="E5" t="n">
-        <v>2.090270615345486</v>
+        <v>19.3859720447272</v>
       </c>
       <c r="F5" t="n">
-        <v>19.3859831369337</v>
+        <v>4.402950379544062</v>
       </c>
       <c r="G5" t="n">
-        <v>4.402951639177258</v>
+        <v>4089.975138452922</v>
       </c>
       <c r="H5" t="n">
-        <v>4089.976425866724</v>
+        <v>1756.902125380605</v>
       </c>
       <c r="I5" t="n">
-        <v>1756.903130632651</v>
+        <v>86.25554399474109</v>
       </c>
       <c r="J5" t="n">
-        <v>86.25555601045376</v>
-      </c>
-      <c r="K5" t="n">
-        <v>98.78982526313484</v>
+        <v>98.78981324742216</v>
       </c>
     </row>
     <row r="6">
@@ -874,37 +911,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>raw\BR07.xls</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-8495.224266188348</v>
       </c>
       <c r="D6" t="n">
-        <v>-8495.224759197712</v>
+        <v>10.59477089805591</v>
       </c>
       <c r="E6" t="n">
-        <v>10.59477149757934</v>
+        <v>362.1690118024043</v>
       </c>
       <c r="F6" t="n">
-        <v>362.1690328179412</v>
+        <v>19.03073860370123</v>
       </c>
       <c r="G6" t="n">
-        <v>19.03073915584839</v>
+        <v>5541.194454349922</v>
       </c>
       <c r="H6" t="n">
-        <v>5541.194827780638</v>
+        <v>5604.783176236376</v>
       </c>
       <c r="I6" t="n">
-        <v>5604.783501463746</v>
+        <v>183.0869966301451</v>
       </c>
       <c r="J6" t="n">
-        <v>183.0869981968707</v>
-      </c>
-      <c r="K6" t="n">
-        <v>198.6370405889227</v>
+        <v>198.637039022197</v>
       </c>
     </row>
     <row r="7">
@@ -915,1021 +947,1328 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>raw\BR08.xls</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.7260378835251096</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7260602469572479</v>
+        <v>0.1656088538391035</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1656098405553068</v>
+        <v>0.06518484944504455</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06518569401338857</v>
+        <v>0.2553132378962057</v>
       </c>
       <c r="G7" t="n">
-        <v>0.255314891875481</v>
+        <v>99.9752846310935</v>
       </c>
       <c r="H7" t="n">
-        <v>99.97577205024716</v>
+        <v>1.138881519338128</v>
       </c>
       <c r="I7" t="n">
-        <v>1.138896119793093</v>
+        <v>-44.26320518816271</v>
       </c>
       <c r="J7" t="n">
-        <v>-44.26288127743808</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-29.63637137901968</v>
+        <v>-29.63669528974431</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw\BR02.xls</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.405059409469512</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4463648571956385</v>
+        <v>0.3761888859996634</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4559543323382335</v>
+        <v>0.2770427244840178</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6735207968885133</v>
+        <v>0.5263484819812989</v>
       </c>
       <c r="G8" t="n">
-        <v>0.820683128185607</v>
+        <v>124.1382490127242</v>
       </c>
       <c r="H8" t="n">
-        <v>99.99906338545736</v>
+        <v>0.3784120842979589</v>
       </c>
       <c r="I8" t="n">
-        <v>1.822748029961302</v>
+        <v>2.179079740540946</v>
       </c>
       <c r="J8" t="n">
-        <v>17.28098111867805</v>
-      </c>
-      <c r="K8" t="n">
-        <v>27.27954124735265</v>
+        <v>12.17763986921554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw\BR03.xls</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4569119949376687</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.322882516113336</v>
+        <v>0.1994289485119298</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3581282369858643</v>
+        <v>0.2157261592602703</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5254772001840454</v>
+        <v>0.4644633023827289</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7248980619259824</v>
+        <v>49.11569413965922</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>0.3199347130008886</v>
       </c>
       <c r="I9" t="n">
-        <v>1.541397589925665</v>
+        <v>0.9938181477767785</v>
       </c>
       <c r="J9" t="n">
-        <v>14.34827285240432</v>
-      </c>
-      <c r="K9" t="n">
-        <v>22.84487526563084</v>
+        <v>9.490420561003297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw\BR04.xls</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7792027177030534</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3230718182399341</v>
+        <v>0.02825197564031457</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06512401722731298</v>
+        <v>0.002898524747240203</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01736867577195525</v>
+        <v>0.05383794895090454</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1317902719169941</v>
+        <v>48.76817297939469</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>0.07426815201215214</v>
       </c>
       <c r="I10" t="n">
-        <v>0.830159237024698</v>
+        <v>-98.71462096474667</v>
       </c>
       <c r="J10" t="n">
-        <v>-61.1148257008888</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-48.58055644820772</v>
+        <v>-86.1803517120656</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw\BR05.xls</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3784041156291683</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3384680361618866</v>
+        <v>0.03316848163507483</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04770749428804517</v>
+        <v>0.004179878737854902</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00900043617778175</v>
+        <v>0.06465198170091077</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09487062863595745</v>
+        <v>71.03384014632016</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>0.195404680427748</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8276814323460264</v>
+        <v>-91.02693390192547</v>
       </c>
       <c r="J11" t="n">
-        <v>-74.92012701106823</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-62.38585775838715</v>
+        <v>-78.4926646492444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw\BR07.xls</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-2.82733323353798</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6979931889262585</v>
+        <v>0.230417727928458</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1724917199622034</v>
+        <v>0.1631479409677605</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07238044759810999</v>
+        <v>0.4039157597417567</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2690361455234407</v>
+        <v>124.0482810068596</v>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>2.536807057477653</v>
       </c>
       <c r="I12" t="n">
-        <v>1.132128539993109</v>
+        <v>-24.95364266571955</v>
       </c>
       <c r="J12" t="n">
-        <v>-46.897115075302</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-31.34707268325005</v>
+        <v>-9.4036002736676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw\BR08.xls</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-5.566526254944699</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7264614927899111</v>
+        <v>0.3415530646556424</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1656358997001203</v>
+        <v>0.2479887778774094</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06520084730141443</v>
+        <v>0.4979847165098638</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2553445658349017</v>
+        <v>218.8923788953765</v>
       </c>
       <c r="H13" t="n">
-        <v>100</v>
+        <v>4.299100041995193</v>
       </c>
       <c r="I13" t="n">
-        <v>1.139158081895927</v>
+        <v>-10.85929460838265</v>
       </c>
       <c r="J13" t="n">
-        <v>-44.25707036783757</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-29.63056046941917</v>
+        <v>3.76721529003575</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw\BR02.xls</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6959067513738362</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4464666394468091</v>
+        <v>0.2823865924302063</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4559645527106111</v>
+        <v>0.1416054366394268</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6735681932716434</v>
+        <v>0.3763049782283339</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8207120038549719</v>
+        <v>87.11669260221817</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>0.1963517802354479</v>
       </c>
       <c r="I14" t="n">
-        <v>1.822875454248386</v>
+        <v>-9.230081969926559</v>
       </c>
       <c r="J14" t="n">
-        <v>17.28217738487788</v>
-      </c>
-      <c r="K14" t="n">
-        <v>27.28073751355248</v>
+        <v>0.7684781587480387</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw\BR03.xls</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8323785062100035</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.322882516113336</v>
+        <v>0.1326929580151907</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3581282369858643</v>
+        <v>0.06658283874385143</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5254772001840454</v>
+        <v>0.2580365066106954</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7248980619259824</v>
+        <v>43.24760948028263</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>0.102894435257695</v>
       </c>
       <c r="I15" t="n">
-        <v>1.541397589925665</v>
+        <v>-16.63962616738259</v>
       </c>
       <c r="J15" t="n">
-        <v>14.34827285240432</v>
-      </c>
-      <c r="K15" t="n">
-        <v>22.84487526563084</v>
+        <v>-8.143023754156069</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw\BR04.xls</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9314612588762474</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3230718182399341</v>
+        <v>0.01764631831778212</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06512401722731298</v>
+        <v>0.0008997449390011536</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01736867577195525</v>
+        <v>0.02999574868212417</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1317902719169941</v>
+        <v>29.55446766253117</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>0.02719144379442658</v>
       </c>
       <c r="I16" t="n">
-        <v>0.830159237024698</v>
+        <v>-123.281383954225</v>
       </c>
       <c r="J16" t="n">
-        <v>-61.1148257008888</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-48.58055644820772</v>
+        <v>-110.7471147015439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw\BR05.xls</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7675824687007322</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3384680361618866</v>
+        <v>0.02248265529181081</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04770749428804517</v>
+        <v>0.001562875691118592</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00900043617778175</v>
+        <v>0.03953322262500986</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09487062863595745</v>
+        <v>44.14768943932386</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>0.07681927237356337</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8276814323460264</v>
+        <v>-111.6857830217282</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.92012701106823</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-62.38585775838715</v>
+        <v>-99.15151376904717</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw\BR07.xls</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.868701925042769</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6774145733282249</v>
+        <v>0.04493206108893516</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1712495839532497</v>
+        <v>0.005596850150019828</v>
       </c>
       <c r="F18" t="n">
-        <v>0.07150324183683304</v>
+        <v>0.07481209895478022</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2674009009648865</v>
+        <v>29.38420145609948</v>
       </c>
       <c r="H18" t="n">
-        <v>98.98213627887546</v>
+        <v>0.04930721759218318</v>
       </c>
       <c r="I18" t="n">
-        <v>1.118553282568501</v>
+        <v>-116.0098854428778</v>
       </c>
       <c r="J18" t="n">
-        <v>-47.22633722823775</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-31.6762948361858</v>
+        <v>-100.4598430508259</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw\BR08.xls</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.6861291932120404</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7264614927899111</v>
+        <v>0.1630606677301762</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1656358997001203</v>
+        <v>0.06367767396851713</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06520084730141443</v>
+        <v>0.2523443559276037</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2553445658349017</v>
+        <v>97.62991140105275</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>1.112826259483148</v>
       </c>
       <c r="I19" t="n">
-        <v>1.139158081895927</v>
+        <v>-44.84803162473584</v>
       </c>
       <c r="J19" t="n">
-        <v>-44.25707036783757</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-29.63056046941917</v>
+        <v>-30.22152172631743</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>raw\BR02.xls</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.335382136305449</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4464666394468091</v>
+        <v>0.6551101574506073</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4559645527106111</v>
+        <v>1.087504601386265</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6735681932716434</v>
+        <v>1.042834886924227</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8207120038549719</v>
+        <v>181.8582085862883</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>2.93573572372404</v>
       </c>
       <c r="I20" t="n">
-        <v>1.822875454248386</v>
+        <v>25.42605715723609</v>
       </c>
       <c r="J20" t="n">
-        <v>17.28217738487788</v>
-      </c>
-      <c r="K20" t="n">
-        <v>27.28073751355248</v>
+        <v>35.42461728591068</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw\BR03.xls</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.8171473407119696</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.322882516113336</v>
+        <v>0.4719724766552892</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3581282369858643</v>
+        <v>0.7218097490052566</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5254772001840454</v>
+        <v>0.849593872980059</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7248980619259824</v>
+        <v>163.5752881087331</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>2.112822053034541</v>
       </c>
       <c r="I21" t="n">
-        <v>1.541397589925665</v>
+        <v>19.11009479481181</v>
       </c>
       <c r="J21" t="n">
-        <v>14.34827285240432</v>
-      </c>
-      <c r="K21" t="n">
-        <v>22.84487526563084</v>
+        <v>27.60669720803833</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>raw\BR04.xls</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6836428606587827</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3230718182399341</v>
+        <v>0.03276077108319422</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06512401722731298</v>
+        <v>0.004152990416401136</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01736867577195525</v>
+        <v>0.06444369958654714</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1317902719169941</v>
+        <v>53.75624464071554</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>0.103814235093846</v>
       </c>
       <c r="I22" t="n">
-        <v>0.830159237024698</v>
+        <v>-91.16245906134786</v>
       </c>
       <c r="J22" t="n">
-        <v>-61.1148257008888</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-48.58055644820772</v>
+        <v>-78.62818980866678</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>raw\BR05.xls</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4981168898774797</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3384680361618866</v>
+        <v>0.02976481484401816</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04770749428804517</v>
+        <v>0.003374878427666842</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00900043617778175</v>
+        <v>0.05809370385564034</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09487062863595745</v>
+        <v>64.82240961985829</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>0.1589273479361229</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8276814323460264</v>
+        <v>-95.51931551150805</v>
       </c>
       <c r="J23" t="n">
-        <v>-74.92012701106823</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-62.38585775838715</v>
+        <v>-82.98504625882697</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>raw\BR07.xls</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8333376535824276</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6979931889262585</v>
+        <v>0.04916163128099967</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1724917199622034</v>
+        <v>0.00710432486427308</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07238044759810999</v>
+        <v>0.08428715717280469</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2690361455234407</v>
+        <v>33.05883575222784</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>0.06097173133026287</v>
       </c>
       <c r="I24" t="n">
-        <v>1.132128539993109</v>
+        <v>-109.5703917033811</v>
       </c>
       <c r="J24" t="n">
-        <v>-46.897115075302</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-31.34707268325005</v>
+        <v>-94.0203493113292</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>raw\BR08.xls</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.7210850773663313</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7264614927899111</v>
+        <v>0.1653888780007226</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1656358997001203</v>
+        <v>0.06499780376842758</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06520084730141443</v>
+        <v>0.2549466684787773</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2553445658349017</v>
+        <v>99.87307727494161</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>1.135647971695597</v>
       </c>
       <c r="I25" t="n">
-        <v>1.139158081895927</v>
+        <v>-44.33504494588426</v>
       </c>
       <c r="J25" t="n">
-        <v>-44.25707036783757</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-29.63056046941917</v>
+        <v>-29.70853504746586</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>induction_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>raw\BR02.xls</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6617487234902701</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4464666394468091</v>
+        <v>0.2391850996144047</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4559645527106111</v>
+        <v>0.1575116182960292</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6735681932716434</v>
+        <v>0.3968773340668741</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8207120038549719</v>
+        <v>73.48731658496781</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>0.2177335157601394</v>
       </c>
       <c r="I26" t="n">
-        <v>1.822875454248386</v>
+        <v>-7.420352960129094</v>
       </c>
       <c r="J26" t="n">
-        <v>17.28217738487788</v>
-      </c>
-      <c r="K26" t="n">
-        <v>27.28073751355248</v>
+        <v>2.578207168545504</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>induction_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>raw\BR03.xls</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5527391750989639</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.322882516113336</v>
+        <v>0.2136913259453583</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3581282369858643</v>
+        <v>0.1776615558511679</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5254772001840454</v>
+        <v>0.4214991765723486</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7248980619259824</v>
+        <v>75.05412442183818</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>0.2645413365661284</v>
       </c>
       <c r="I27" t="n">
-        <v>1.541397589925665</v>
+        <v>-1.918123653214327</v>
       </c>
       <c r="J27" t="n">
-        <v>14.34827285240432</v>
-      </c>
-      <c r="K27" t="n">
-        <v>22.84487526563084</v>
+        <v>6.578478760012192</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>induction_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>raw\BR04.xls</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8992551373855979</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3230718182399341</v>
+        <v>0.01849725671003058</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06512401722731298</v>
+        <v>0.00132253202760185</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01736867577195525</v>
+        <v>0.03636663343783488</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1317902719169941</v>
+        <v>32.98626378490538</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>0.03714923120364192</v>
       </c>
       <c r="I28" t="n">
-        <v>0.830159237024698</v>
+        <v>-115.1923507181916</v>
       </c>
       <c r="J28" t="n">
-        <v>-61.1148257008888</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-48.58055644820772</v>
+        <v>-102.6580814655105</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>induction_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>raw\BR05.xls</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8881220432082013</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3384680361618866</v>
+        <v>0.01370480841839532</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04770749428804517</v>
+        <v>0.0007523156194993499</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00900043617778175</v>
+        <v>0.02742837252735477</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09487062863595745</v>
+        <v>33.19274328850599</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>0.04009000797118915</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8276814323460264</v>
+        <v>-127.0394469209984</v>
       </c>
       <c r="J29" t="n">
-        <v>-74.92012701106823</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-62.38585775838715</v>
+        <v>-114.5051776683173</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>induction_rP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>raw\BR07.xls</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8629836216486066</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6979931889262585</v>
+        <v>0.04583827576830698</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1724917199622034</v>
+        <v>0.005840604578406549</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07238044759810999</v>
+        <v>0.07642384823081437</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2690361455234407</v>
+        <v>30.84565432350142</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>0.05119333671030259</v>
       </c>
       <c r="I30" t="n">
-        <v>1.132128539993109</v>
+        <v>-114.8588660226124</v>
       </c>
       <c r="J30" t="n">
-        <v>-46.897115075302</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-31.34707268325005</v>
+        <v>-99.30882363056043</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>global_ind_rP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.7247381822543337</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1655554504251596</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.06513576545189022</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2552170947485498</v>
+      </c>
+      <c r="G31" t="n">
+        <v>99.95807674080191</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.138032980985247</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-44.2820372031567</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-29.6555273047383</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>induction_qP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.2839456901969291</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4870770731117862</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5978879534585083</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.7732321471967577</v>
+      </c>
+      <c r="G32" t="n">
+        <v>141.2372544838753</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.619410548960069</v>
+      </c>
+      <c r="I32" t="n">
+        <v>15.25601750644288</v>
+      </c>
+      <c r="J32" t="n">
+        <v>25.25457763511748</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>induction_qP</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1932741919878278</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.3064797969734007</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3204487274923888</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5660819088191997</v>
+      </c>
+      <c r="G33" t="n">
+        <v>113.0531453271593</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4723318516483238</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.929505119372266</v>
+      </c>
+      <c r="J33" t="n">
+        <v>15.42610753259878</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>induction_qP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.845444048742398</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.02305237396074036</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.002028939146773209</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.04504374703300347</v>
+      </c>
+      <c r="G34" t="n">
+        <v>39.72229544693047</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.05378704278002185</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-106.2050864167512</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-93.67081716407009</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>induction_qP</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7150262643130276</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0224287367245416</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.001916286269898207</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.04377540713572185</v>
+      </c>
+      <c r="G35" t="n">
+        <v>49.31135257773587</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.09283352109502048</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-107.4046902087683</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-94.87042095608726</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>induction_qP</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5641875820571072</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08140493220742497</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.01857739953566509</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1362989344626916</v>
+      </c>
+      <c r="G36" t="n">
+        <v>50.29361203499592</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1497479050578334</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-83.61685692652858</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-68.06681453447663</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>induction_qP</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.4100531508899652</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1494199258929221</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.05325149768008318</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2307628602701985</v>
+      </c>
+      <c r="G37" t="n">
+        <v>91.76513886233147</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.9325839872860957</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-49.31823373351361</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-34.6917238350952</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>induction_rP</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>raw\BR08.xls</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.06676708920238184</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.1124618005351112</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.03524409711290005</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.1877341128109115</v>
-      </c>
-      <c r="H31" t="n">
-        <v>66.25092691877812</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.3106407412183155</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-59.63643053841375</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-45.00992063999534</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BR02</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6451944888413121</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.2453527026388743</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1652203380268609</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.4064730471099663</v>
+      </c>
+      <c r="G38" t="n">
+        <v>79.24936105555602</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.228095889966409</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-6.608080336812073</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.390479791862525</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>induction_rP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BR03</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-4.748439183636087</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.7763954847524154</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.283402865222053</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.51109326820751</v>
+      </c>
+      <c r="G39" t="n">
+        <v>216.3068701343592</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.657827521492527</v>
+      </c>
+      <c r="I39" t="n">
+        <v>36.38500222596662</v>
+      </c>
+      <c r="J39" t="n">
+        <v>44.88160463919314</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>induction_rP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BR04</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.9734808402279989</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.008174724025868663</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000348131281669426</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.01865827649246913</v>
+      </c>
+      <c r="G40" t="n">
+        <v>18.10382116191152</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.01419943982876894</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-143.2215489662075</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-130.6872797135264</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>induction_rP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BR05</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.9415712352880893</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.007512055988646149</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0003929002064510812</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.01982171048247555</v>
+      </c>
+      <c r="G41" t="n">
+        <v>14.71304895593737</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.02380365955808898</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-140.681053024855</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-128.146783772174</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>induction_rP</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BR07</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6277334277887661</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.07321103709252057</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.01586862732912495</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.1259707399721259</v>
+      </c>
+      <c r="G42" t="n">
+        <v>45.69831734977994</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1287880107937577</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-87.87210355786321</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-72.32206116581126</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>induction_rP</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BR08</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.8341141269535439</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.04566264031759223</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.006264778868879159</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.07915035608813872</v>
+      </c>
+      <c r="G43" t="n">
+        <v>39.09883312053942</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.06015110712215224</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-102.8202996881331</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-88.1937897897147</v>
       </c>
     </row>
   </sheetData>

--- a/results/modelling/metrics_summary_all_models.xlsx
+++ b/results/modelling/metrics_summary_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,218 +479,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parametric</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6858376492188204</v>
+        <v>0.9270681812472175</v>
       </c>
       <c r="C2" t="n">
-        <v>1.674785349640658</v>
+        <v>0.8376590455220122</v>
       </c>
       <c r="D2" t="n">
-        <v>29.59510740595649</v>
+        <v>6.870412714742317</v>
       </c>
       <c r="E2" t="n">
-        <v>5.440138546577329</v>
+        <v>2.621147213481593</v>
       </c>
       <c r="F2" t="n">
-        <v>426.1993360172079</v>
+        <v>37.81407750429122</v>
       </c>
       <c r="G2" t="n">
-        <v>20.8168238894039</v>
+        <v>4.837168445945456</v>
       </c>
       <c r="H2" t="n">
-        <v>1731.354964893692</v>
+        <v>995.3209863953904</v>
       </c>
       <c r="I2" t="n">
-        <v>1782.025880110548</v>
+        <v>1045.991901612247</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9276767947032194</v>
+        <v>0.9275113039323916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8143521485957379</v>
+        <v>0.8075710004045736</v>
       </c>
       <c r="D3" t="n">
-        <v>6.813079362880449</v>
+        <v>6.828669127615681</v>
       </c>
       <c r="E3" t="n">
-        <v>2.610187610667182</v>
+        <v>2.61317223458686</v>
       </c>
       <c r="F3" t="n">
-        <v>33.38578452227281</v>
+        <v>24.88941681861841</v>
       </c>
       <c r="G3" t="n">
-        <v>4.796852515605349</v>
+        <v>4.807814998151259</v>
       </c>
       <c r="H3" t="n">
-        <v>991.0974770347943</v>
+        <v>992.2494180565071</v>
       </c>
       <c r="I3" t="n">
-        <v>1041.768392251651</v>
+        <v>1042.920333273364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9279610434322036</v>
+        <v>0.927696051297303</v>
       </c>
       <c r="C4" t="n">
-        <v>0.789528458579741</v>
+        <v>0.8023529234808232</v>
       </c>
       <c r="D4" t="n">
-        <v>6.786302215194306</v>
+        <v>6.811265329566909</v>
       </c>
       <c r="E4" t="n">
-        <v>2.605053207747263</v>
+        <v>2.609840096551302</v>
       </c>
       <c r="F4" t="n">
-        <v>23.19477703264317</v>
+        <v>25.86940428895298</v>
       </c>
       <c r="G4" t="n">
-        <v>4.778023237606353</v>
+        <v>4.795576915307645</v>
       </c>
       <c r="H4" t="n">
-        <v>989.1127250374955</v>
+        <v>990.9632653987758</v>
       </c>
       <c r="I4" t="n">
-        <v>1039.783640254352</v>
+        <v>1041.634180615632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9274113015424745</v>
+        <v>0.9278610086645291</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8134729904131718</v>
+        <v>0.7934391308069343</v>
       </c>
       <c r="D5" t="n">
-        <v>6.838089675504649</v>
+        <v>6.79572581317253</v>
       </c>
       <c r="E5" t="n">
-        <v>2.614974125207485</v>
+        <v>2.606861295345905</v>
       </c>
       <c r="F5" t="n">
-        <v>28.4637293293266</v>
+        <v>24.11907166496622</v>
       </c>
       <c r="G5" t="n">
-        <v>4.814439382390512</v>
+        <v>4.784649766621413</v>
       </c>
       <c r="H5" t="n">
-        <v>992.944236331479</v>
+        <v>989.8121042661699</v>
       </c>
       <c r="I5" t="n">
-        <v>1043.615151548335</v>
+        <v>1040.483019483026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9279192672449763</v>
+        <v>0.9277123813336965</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7903234480988496</v>
+        <v>0.8045506363235463</v>
       </c>
       <c r="D6" t="n">
-        <v>6.79023766686421</v>
+        <v>6.80972698743328</v>
       </c>
       <c r="E6" t="n">
-        <v>2.605808447845737</v>
+        <v>2.609545360294256</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44910777600707</v>
+        <v>27.43800133418387</v>
       </c>
       <c r="G6" t="n">
-        <v>4.780790586631454</v>
+        <v>4.794495176803187</v>
       </c>
       <c r="H6" t="n">
-        <v>989.4049154946247</v>
+        <v>990.8494228209955</v>
       </c>
       <c r="I6" t="n">
-        <v>1040.075830711481</v>
+        <v>1041.520338037852</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9277146686156172</v>
+        <v>0.9271775703264432</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8031048113699013</v>
+        <v>0.823596511951921</v>
       </c>
       <c r="D7" t="n">
-        <v>6.809511518094115</v>
+        <v>6.860107910424815</v>
       </c>
       <c r="E7" t="n">
-        <v>2.609504075125026</v>
+        <v>2.61918077085657</v>
       </c>
       <c r="F7" t="n">
-        <v>26.46133930617218</v>
+        <v>40.61314256095522</v>
       </c>
       <c r="G7" t="n">
-        <v>4.794343662081195</v>
+        <v>4.829922266199437</v>
       </c>
       <c r="H7" t="n">
-        <v>990.8334752998616</v>
+        <v>994.5644786863362</v>
       </c>
       <c r="I7" t="n">
-        <v>1041.504390516718</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9272771322676369</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.8021099342463233</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.850728854227143</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.617389702399538</v>
-      </c>
-      <c r="F8" t="n">
-        <v>23.54852011162094</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4.823327058278709</v>
-      </c>
-      <c r="H8" t="n">
-        <v>993.874944540158</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1044.545859757015</v>
+        <v>1045.235393903193</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +731,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parametric</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -771,34 +740,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.02647133941943491</v>
+        <v>0.09574960298759028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4145297220830514</v>
+        <v>0.4684113267839541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4779912835060565</v>
+        <v>0.4210773270331013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6913691369348623</v>
+        <v>0.6489047133694602</v>
       </c>
       <c r="G2" t="n">
-        <v>275.8946235261489</v>
+        <v>150.9957183062228</v>
       </c>
       <c r="H2" t="n">
-        <v>1.29707060056014</v>
+        <v>0.5720292480268938</v>
       </c>
       <c r="I2" t="n">
-        <v>11.45123270600128</v>
+        <v>9.296040612450142</v>
       </c>
       <c r="J2" t="n">
-        <v>21.44979283467588</v>
+        <v>19.29460074112474</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>parametric</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -807,34 +776,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-67.00228262484909</v>
+        <v>-1.508408329309784</v>
       </c>
       <c r="D3" t="n">
-        <v>3.022410473726135</v>
+        <v>0.5404033116847669</v>
       </c>
       <c r="E3" t="n">
-        <v>27.01195959926681</v>
+        <v>0.9963933831982982</v>
       </c>
       <c r="F3" t="n">
-        <v>5.197303108273252</v>
+        <v>0.9981950626998203</v>
       </c>
       <c r="G3" t="n">
-        <v>1101.546535684024</v>
+        <v>170.5713817219281</v>
       </c>
       <c r="H3" t="n">
-        <v>78.63011301388299</v>
+        <v>2.911995734063488</v>
       </c>
       <c r="I3" t="n">
-        <v>73.44419574079143</v>
+        <v>23.94580295513381</v>
       </c>
       <c r="J3" t="n">
-        <v>81.94079815401795</v>
+        <v>32.44240536836033</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>parametric</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -843,34 +812,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-3264.48404192818</v>
+        <v>0.9103874789246301</v>
       </c>
       <c r="D4" t="n">
-        <v>3.457857740383385</v>
+        <v>0.01627718815436799</v>
       </c>
       <c r="E4" t="n">
-        <v>42.86776634559004</v>
+        <v>0.001176391789325641</v>
       </c>
       <c r="F4" t="n">
-        <v>6.547348039136918</v>
+        <v>0.03429856832763783</v>
       </c>
       <c r="G4" t="n">
-        <v>6033.09380528493</v>
+        <v>25.30189591078712</v>
       </c>
       <c r="H4" t="n">
-        <v>2019.317298040734</v>
+        <v>0.03370723057513891</v>
       </c>
       <c r="I4" t="n">
-        <v>102.9205237018899</v>
+        <v>-117.6513699468161</v>
       </c>
       <c r="J4" t="n">
-        <v>115.454792954571</v>
+        <v>-105.117100694135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>parametric</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -879,34 +848,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2881.916274196644</v>
+        <v>0.8694745308790788</v>
       </c>
       <c r="D5" t="n">
-        <v>2.090269996544669</v>
+        <v>0.01499824454961553</v>
       </c>
       <c r="E5" t="n">
-        <v>19.3859720447272</v>
+        <v>0.0008777095325837012</v>
       </c>
       <c r="F5" t="n">
-        <v>4.402950379544062</v>
+        <v>0.02962616297436611</v>
       </c>
       <c r="G5" t="n">
-        <v>4089.975138452922</v>
+        <v>35.66417476763733</v>
       </c>
       <c r="H5" t="n">
-        <v>1756.902125380605</v>
+        <v>0.04577203740908496</v>
       </c>
       <c r="I5" t="n">
-        <v>86.25554399474109</v>
+        <v>-123.8020917987042</v>
       </c>
       <c r="J5" t="n">
-        <v>98.78981324742216</v>
+        <v>-111.2678225460231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>parametric</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -915,34 +884,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-8495.224266188348</v>
+        <v>-4.089543194805494</v>
       </c>
       <c r="D6" t="n">
-        <v>10.59477089805591</v>
+        <v>0.2636684898342958</v>
       </c>
       <c r="E6" t="n">
-        <v>362.1690118024043</v>
+        <v>0.2169522333260282</v>
       </c>
       <c r="F6" t="n">
-        <v>19.03073860370123</v>
+        <v>0.4657813149172348</v>
       </c>
       <c r="G6" t="n">
-        <v>5541.194454349922</v>
+        <v>137.4578530551209</v>
       </c>
       <c r="H6" t="n">
-        <v>5604.783176236376</v>
+        <v>3.369459043539736</v>
       </c>
       <c r="I6" t="n">
-        <v>183.0869966301451</v>
+        <v>-17.25810796003294</v>
       </c>
       <c r="J6" t="n">
-        <v>198.637039022197</v>
+        <v>-1.708065567980988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>parametric</t>
+          <t>global_qP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,34 +920,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.7260378835251096</v>
+        <v>-19.73335964911068</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1656088538391035</v>
+        <v>0.5334563431121593</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06518484944504455</v>
+        <v>0.7830076848933658</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2553132378962057</v>
+        <v>0.8848772145859367</v>
       </c>
       <c r="G7" t="n">
-        <v>99.9752846310935</v>
+        <v>274.0146414187547</v>
       </c>
       <c r="H7" t="n">
-        <v>1.138881519338128</v>
+        <v>13.54822654831712</v>
       </c>
       <c r="I7" t="n">
-        <v>-44.26320518816271</v>
+        <v>17.88468079097826</v>
       </c>
       <c r="J7" t="n">
-        <v>-29.63669528974431</v>
+        <v>32.51119068939667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -987,34 +956,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.405059409469512</v>
+        <v>-1.512372893626789</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3761888859996634</v>
+        <v>0.7719567964449554</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2770427244840178</v>
+        <v>1.169922917428664</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5263484819812989</v>
+        <v>1.081629750621101</v>
       </c>
       <c r="G8" t="n">
-        <v>124.1382490127242</v>
+        <v>245.2807266599923</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3784120842979589</v>
+        <v>3.157315820576204</v>
       </c>
       <c r="I8" t="n">
-        <v>2.179079740540946</v>
+        <v>26.6679436896951</v>
       </c>
       <c r="J8" t="n">
-        <v>12.17763986921554</v>
+        <v>36.6665038183697</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1023,34 +992,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4569119949376687</v>
+        <v>-0.05723324559225973</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1994289485119298</v>
+        <v>0.3639767187409497</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2157261592602703</v>
+        <v>0.4199556340555006</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4644633023827289</v>
+        <v>0.6480398398675042</v>
       </c>
       <c r="G9" t="n">
-        <v>49.11569413965922</v>
+        <v>119.2410682500004</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3199347130008886</v>
+        <v>1.234277835033057</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9938181477767785</v>
+        <v>10.98590690271763</v>
       </c>
       <c r="J9" t="n">
-        <v>9.490420561003297</v>
+        <v>19.48250931594414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1059,34 +1028,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7792027177030534</v>
+        <v>0.7812119610603125</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02825197564031457</v>
+        <v>0.03074004103229599</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002898524747240203</v>
+        <v>0.002872148328410865</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05383794895090454</v>
+        <v>0.05359242790181151</v>
       </c>
       <c r="G10" t="n">
-        <v>48.76817297939469</v>
+        <v>47.35683526760635</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07426815201215214</v>
+        <v>0.07364691551179385</v>
       </c>
       <c r="I10" t="n">
-        <v>-98.71462096474667</v>
+        <v>-98.90659463769067</v>
       </c>
       <c r="J10" t="n">
-        <v>-86.1803517120656</v>
+        <v>-86.37232538500959</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1095,34 +1064,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3784041156291683</v>
+        <v>0.9634663048279452</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03316848163507483</v>
+        <v>0.007692773660925684</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004179878737854902</v>
+        <v>0.0002456683184437606</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06465198170091077</v>
+        <v>0.01567380995303186</v>
       </c>
       <c r="G11" t="n">
-        <v>71.03384014632016</v>
+        <v>19.04063946593572</v>
       </c>
       <c r="H11" t="n">
-        <v>0.195404680427748</v>
+        <v>0.01713207637452709</v>
       </c>
       <c r="I11" t="n">
-        <v>-91.02693390192547</v>
+        <v>-150.5420928470936</v>
       </c>
       <c r="J11" t="n">
-        <v>-78.4926646492444</v>
+        <v>-138.0078235944125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,34 +1100,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.82733323353798</v>
+        <v>0.7944626915715153</v>
       </c>
       <c r="D12" t="n">
-        <v>0.230417727928458</v>
+        <v>0.07329312703159553</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1631479409677605</v>
+        <v>0.008761449974703397</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4039157597417567</v>
+        <v>0.09360261734964144</v>
       </c>
       <c r="G12" t="n">
-        <v>124.0482810068596</v>
+        <v>33.80243664617695</v>
       </c>
       <c r="H12" t="n">
-        <v>2.536807057477653</v>
+        <v>0.0737942075108378</v>
       </c>
       <c r="I12" t="n">
-        <v>-24.95364266571955</v>
+        <v>-103.9096343686273</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.4036002736676</v>
+        <v>-88.35959197657533</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>global_qP</t>
+          <t>global_rP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1167,34 +1136,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-5.566526254944699</v>
+        <v>0.9455290384443344</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3415530646556424</v>
+        <v>0.02591958065107009</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2479887778774094</v>
+        <v>0.002057128329582933</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4979847165098638</v>
+        <v>0.04535557660952987</v>
       </c>
       <c r="G13" t="n">
-        <v>218.8923788953765</v>
+        <v>15.71296596866016</v>
       </c>
       <c r="H13" t="n">
-        <v>4.299100041995193</v>
+        <v>0.02378127829740772</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.85929460838265</v>
+        <v>-130.6611070872182</v>
       </c>
       <c r="J13" t="n">
-        <v>3.76721529003575</v>
+        <v>-116.0345971887998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1203,34 +1172,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6959067513738362</v>
+        <v>0.4585448127154184</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2823865924302063</v>
+        <v>0.3014193885503887</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1416054366394268</v>
+        <v>0.252136469857552</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3763049782283339</v>
+        <v>0.5021319247543936</v>
       </c>
       <c r="G14" t="n">
-        <v>87.11669260221817</v>
+        <v>74.90406082963577</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1963517802354479</v>
+        <v>0.3449320850856609</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.230081969926559</v>
+        <v>0.5776585529894156</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7684781587480387</v>
+        <v>10.57621868166401</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1239,34 +1208,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8323785062100035</v>
+        <v>-0.6710224551005455</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1326929580151907</v>
+        <v>0.4500227168460114</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06658283874385143</v>
+        <v>0.6637658223276993</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2580365066106954</v>
+        <v>0.8147182472043322</v>
       </c>
       <c r="G15" t="n">
-        <v>43.24760948028263</v>
+        <v>154.4435159554785</v>
       </c>
       <c r="H15" t="n">
-        <v>0.102894435257695</v>
+        <v>1.943885624319106</v>
       </c>
       <c r="I15" t="n">
-        <v>-16.63962616738259</v>
+        <v>17.85261196607611</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.143023754156069</v>
+        <v>26.34921437930263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1275,34 +1244,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9314612588762474</v>
+        <v>0.8596366361357661</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01764631831778212</v>
+        <v>0.02199822228195616</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0008997449390011536</v>
+        <v>0.001842625414289302</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02999574868212417</v>
+        <v>0.0429258129135524</v>
       </c>
       <c r="G16" t="n">
-        <v>29.55446766253117</v>
+        <v>42.63592008290396</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02719144379442658</v>
+        <v>0.04939884694927268</v>
       </c>
       <c r="I16" t="n">
-        <v>-123.281383954225</v>
+        <v>-108.2278412439681</v>
       </c>
       <c r="J16" t="n">
-        <v>-110.7471147015439</v>
+        <v>-95.69357199128703</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1311,34 +1280,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7675824687007322</v>
+        <v>0.5703750109802544</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02248265529181081</v>
+        <v>0.0275872885261541</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001562875691118592</v>
+        <v>0.002888983666087874</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03953322262500986</v>
+        <v>0.05374926665627983</v>
       </c>
       <c r="G17" t="n">
-        <v>44.14768943932386</v>
+        <v>60.44288016153562</v>
       </c>
       <c r="H17" t="n">
-        <v>0.07681927237356337</v>
+        <v>0.1369097852721852</v>
       </c>
       <c r="I17" t="n">
-        <v>-111.6857830217282</v>
+        <v>-98.78386073820451</v>
       </c>
       <c r="J17" t="n">
-        <v>-99.15151376904717</v>
+        <v>-86.24959148552344</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1347,34 +1316,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.868701925042769</v>
+        <v>0.8659244031664511</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04493206108893516</v>
+        <v>0.04543805287146676</v>
       </c>
       <c r="E18" t="n">
-        <v>0.005596850150019828</v>
+        <v>0.005715247725423861</v>
       </c>
       <c r="F18" t="n">
-        <v>0.07481209895478022</v>
+        <v>0.07559925743963271</v>
       </c>
       <c r="G18" t="n">
-        <v>29.38420145609948</v>
+        <v>29.91427223456748</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04930721759218318</v>
+        <v>0.05022335245786137</v>
       </c>
       <c r="I18" t="n">
-        <v>-116.0098854428778</v>
+        <v>-115.4446761758863</v>
       </c>
       <c r="J18" t="n">
-        <v>-100.4598430508259</v>
+        <v>-99.89463378383437</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>global_rP</t>
+          <t>global_ind_qP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1383,34 +1352,34 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.6861291932120404</v>
+        <v>-2.467164784220867</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1630606677301762</v>
+        <v>0.2097762040093973</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06367767396851713</v>
+        <v>0.1309395446170749</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2523443559276037</v>
+        <v>0.3618556958472187</v>
       </c>
       <c r="G19" t="n">
-        <v>97.62991140105275</v>
+        <v>110.1638572653397</v>
       </c>
       <c r="H19" t="n">
-        <v>1.112826259483148</v>
+        <v>2.275614232996425</v>
       </c>
       <c r="I19" t="n">
-        <v>-44.84803162473584</v>
+        <v>-26.82548884434149</v>
       </c>
       <c r="J19" t="n">
-        <v>-30.22152172631743</v>
+        <v>-12.19897894592309</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1419,34 +1388,34 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1.335382136305449</v>
+        <v>0.7496952812796226</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6551101574506073</v>
+        <v>0.1983754540057743</v>
       </c>
       <c r="E20" t="n">
-        <v>1.087504601386265</v>
+        <v>0.1165580266824061</v>
       </c>
       <c r="F20" t="n">
-        <v>1.042834886924227</v>
+        <v>0.3414059558390951</v>
       </c>
       <c r="G20" t="n">
-        <v>181.8582085862883</v>
+        <v>66.02850558969024</v>
       </c>
       <c r="H20" t="n">
-        <v>2.93573572372404</v>
+        <v>0.1626820342937975</v>
       </c>
       <c r="I20" t="n">
-        <v>25.42605715723609</v>
+        <v>-12.53922279675291</v>
       </c>
       <c r="J20" t="n">
-        <v>35.42461728591068</v>
+        <v>-2.540662668078312</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1455,34 +1424,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.8171473407119696</v>
+        <v>0.1053138417021298</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4719724766552892</v>
+        <v>0.2946925344207538</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7218097490052566</v>
+        <v>0.3553884579917649</v>
       </c>
       <c r="F21" t="n">
-        <v>0.849593872980059</v>
+        <v>0.5961446619670135</v>
       </c>
       <c r="G21" t="n">
-        <v>163.5752881087331</v>
+        <v>85.03036410907156</v>
       </c>
       <c r="H21" t="n">
-        <v>2.112822053034541</v>
+        <v>0.5231777680835965</v>
       </c>
       <c r="I21" t="n">
-        <v>19.11009479481181</v>
+        <v>8.481842401568938</v>
       </c>
       <c r="J21" t="n">
-        <v>27.60669720803833</v>
+        <v>16.97844481479546</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1491,34 +1460,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6836428606587827</v>
+        <v>0.7931781614022502</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03276077108319422</v>
+        <v>0.02686312194606616</v>
       </c>
       <c r="E22" t="n">
-        <v>0.004152990416401136</v>
+        <v>0.002715061576886026</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06444369958654714</v>
+        <v>0.05210625276189055</v>
       </c>
       <c r="G22" t="n">
-        <v>53.75624464071554</v>
+        <v>48.83463863732342</v>
       </c>
       <c r="H22" t="n">
-        <v>0.103814235093846</v>
+        <v>0.06994709468314518</v>
       </c>
       <c r="I22" t="n">
-        <v>-91.16245906134786</v>
+        <v>-100.0877535576158</v>
       </c>
       <c r="J22" t="n">
-        <v>-78.62818980866678</v>
+        <v>-87.5534843049347</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1527,34 +1496,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4981168898774797</v>
+        <v>0.9317563508669819</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02976481484401816</v>
+        <v>0.01005168355036233</v>
       </c>
       <c r="E23" t="n">
-        <v>0.003374878427666842</v>
+        <v>0.000458899721148343</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05809370385564034</v>
+        <v>0.02142194484981098</v>
       </c>
       <c r="G23" t="n">
-        <v>64.82240961985829</v>
+        <v>25.78214475422084</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1589273479361229</v>
+        <v>0.02679432454470926</v>
       </c>
       <c r="I23" t="n">
-        <v>-95.51931551150805</v>
+        <v>-137.4202557285361</v>
       </c>
       <c r="J23" t="n">
-        <v>-82.98504625882697</v>
+        <v>-124.8859864758551</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1563,34 +1532,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.8333376535824276</v>
+        <v>0.6163548261691991</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04916163128099967</v>
+        <v>0.07489032379967771</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00710432486427308</v>
+        <v>0.0163536635964292</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08428715717280469</v>
+        <v>0.1278814435187107</v>
       </c>
       <c r="G24" t="n">
-        <v>33.05883575222784</v>
+        <v>51.34941941708626</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06097173133026287</v>
+        <v>0.1325411166667407</v>
       </c>
       <c r="I24" t="n">
-        <v>-109.5703917033811</v>
+        <v>-87.05919000621238</v>
       </c>
       <c r="J24" t="n">
-        <v>-94.0203493113292</v>
+        <v>-71.50914761416043</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>global_ind_qP</t>
+          <t>global_ind_rP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1599,34 +1568,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.7210850773663313</v>
+        <v>-1.242824159445016</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1653888780007226</v>
+        <v>0.1721770686733221</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06499780376842758</v>
+        <v>0.08470159117628956</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2549466684787773</v>
+        <v>0.2910353778774834</v>
       </c>
       <c r="G25" t="n">
-        <v>99.87307727494161</v>
+        <v>93.89479442390952</v>
       </c>
       <c r="H25" t="n">
-        <v>1.135647971695597</v>
+        <v>1.476276723313815</v>
       </c>
       <c r="I25" t="n">
-        <v>-44.33504494588426</v>
+        <v>-37.71552228689784</v>
       </c>
       <c r="J25" t="n">
-        <v>-29.70853504746586</v>
+        <v>-23.08901238847943</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1635,34 +1604,34 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6617487234902701</v>
+        <v>-0.2859261344560482</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2391850996144047</v>
+        <v>0.4874603764946395</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1575116182960292</v>
+        <v>0.598810176083705</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3968773340668741</v>
+        <v>0.7738282600704791</v>
       </c>
       <c r="G26" t="n">
-        <v>73.48731658496781</v>
+        <v>141.342357124098</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2177335157601394</v>
+        <v>1.621889927190816</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.420352960129094</v>
+        <v>15.28221924829393</v>
       </c>
       <c r="J26" t="n">
-        <v>2.578207168545504</v>
+        <v>25.28077937696852</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1671,34 +1640,34 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5527391750989639</v>
+        <v>0.2281167138655187</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2136913259453583</v>
+        <v>0.2988997134577832</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1776615558511679</v>
+        <v>0.3066085333552461</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4214991765723486</v>
+        <v>0.5537224334946581</v>
       </c>
       <c r="G27" t="n">
-        <v>75.05412442183818</v>
+        <v>110.625472000129</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2645413365661284</v>
+        <v>0.4521909591890166</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.918123653214327</v>
+        <v>6.267247789157388</v>
       </c>
       <c r="J27" t="n">
-        <v>6.578478760012192</v>
+        <v>14.76385020238391</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1707,34 +1676,34 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8992551373855979</v>
+        <v>0.5474913497187138</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01849725671003058</v>
+        <v>0.03899110654342402</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00132253202760185</v>
+        <v>0.005940324570737293</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03636663343783488</v>
+        <v>0.07707350109302998</v>
       </c>
       <c r="G28" t="n">
-        <v>32.98626378490538</v>
+        <v>62.91604666968036</v>
       </c>
       <c r="H28" t="n">
-        <v>0.03714923120364192</v>
+        <v>0.145910822283902</v>
       </c>
       <c r="I28" t="n">
-        <v>-115.1923507181916</v>
+        <v>-83.64582161680437</v>
       </c>
       <c r="J28" t="n">
-        <v>-102.6580814655105</v>
+        <v>-71.1115523641233</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1743,34 +1712,34 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.8881220432082013</v>
+        <v>0.7706611796375538</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01370480841839532</v>
+        <v>0.0202099603280663</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0007523156194993499</v>
+        <v>0.001542173111342268</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02742837252735477</v>
+        <v>0.03927051198217649</v>
       </c>
       <c r="G29" t="n">
-        <v>33.19274328850599</v>
+        <v>46.06781420264491</v>
       </c>
       <c r="H29" t="n">
-        <v>0.04009000797118915</v>
+        <v>0.07588116728667348</v>
       </c>
       <c r="I29" t="n">
-        <v>-127.0394469209984</v>
+        <v>-111.9658176655223</v>
       </c>
       <c r="J29" t="n">
-        <v>-114.5051776683173</v>
+        <v>-99.43154841284127</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1779,34 +1748,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.8629836216486066</v>
+        <v>0.3888133932402384</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04583827576830698</v>
+        <v>0.09410452583026035</v>
       </c>
       <c r="E30" t="n">
-        <v>0.005840604578406549</v>
+        <v>0.02605308457757469</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07642384823081437</v>
+        <v>0.1614096793181087</v>
       </c>
       <c r="G30" t="n">
-        <v>30.84565432350142</v>
+        <v>61.36778384189272</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05119333671030259</v>
+        <v>0.2075931412322308</v>
       </c>
       <c r="I30" t="n">
-        <v>-114.8588660226124</v>
+        <v>-74.48571591343376</v>
       </c>
       <c r="J30" t="n">
-        <v>-99.30882363056043</v>
+        <v>-58.93567352138182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>global_ind_rP</t>
+          <t>induction_qP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1815,34 +1784,34 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.7247381822543337</v>
+        <v>-0.4353595732050308</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1655554504251596</v>
+        <v>0.1576111673585755</v>
       </c>
       <c r="E31" t="n">
-        <v>0.06513576545189022</v>
+        <v>0.05420720980224777</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2552170947485498</v>
+        <v>0.232824418397744</v>
       </c>
       <c r="G31" t="n">
-        <v>99.95807674080191</v>
+        <v>98.11950393731549</v>
       </c>
       <c r="H31" t="n">
-        <v>1.138032980985247</v>
+        <v>0.9491058376461655</v>
       </c>
       <c r="I31" t="n">
-        <v>-44.2820372031567</v>
+        <v>-48.87353393003772</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.6555273047383</v>
+        <v>-34.24702403161932</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1851,34 +1820,34 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.2839456901969291</v>
+        <v>0.2351195373343529</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4870770731117862</v>
+        <v>0.3732934095087075</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5978879534585083</v>
+        <v>0.3561776934610209</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7732321471967577</v>
+        <v>0.5968062444889639</v>
       </c>
       <c r="G32" t="n">
-        <v>141.2372544838753</v>
+        <v>111.6838062598939</v>
       </c>
       <c r="H32" t="n">
-        <v>1.619410548960069</v>
+        <v>0.4847885242224088</v>
       </c>
       <c r="I32" t="n">
-        <v>15.25601750644288</v>
+        <v>6.450465926708034</v>
       </c>
       <c r="J32" t="n">
-        <v>25.25457763511748</v>
+        <v>16.44902605538263</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1887,34 +1856,34 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1932741919878278</v>
+        <v>-1.944998390510144</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3064797969734007</v>
+        <v>0.5595122116110116</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3204487274923888</v>
+        <v>1.169816283715408</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5660819088191997</v>
+        <v>1.081580456422641</v>
       </c>
       <c r="G33" t="n">
-        <v>113.0531453271593</v>
+        <v>161.2425381176444</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4723318516483238</v>
+        <v>3.416741831507658</v>
       </c>
       <c r="I33" t="n">
-        <v>6.929505119372266</v>
+        <v>26.35270071022325</v>
       </c>
       <c r="J33" t="n">
-        <v>15.42610753259878</v>
+        <v>34.84930312344977</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1923,34 +1892,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.845444048742398</v>
+        <v>-63.01474577056928</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02305237396074036</v>
+        <v>0.4899272583162295</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002028939146773209</v>
+        <v>0.840356017402172</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04504374703300347</v>
+        <v>0.9167093418320619</v>
       </c>
       <c r="G34" t="n">
-        <v>39.72229544693047</v>
+        <v>913.7384704025237</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05378704278002185</v>
+        <v>39.59734588670461</v>
       </c>
       <c r="I34" t="n">
-        <v>-106.2050864167512</v>
+        <v>20.34747741940997</v>
       </c>
       <c r="J34" t="n">
-        <v>-93.67081716407009</v>
+        <v>32.88174667209105</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1959,34 +1928,34 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.7150262643130276</v>
+        <v>0.8983323569561459</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0224287367245416</v>
+        <v>0.01286726035318185</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001916286269898207</v>
+        <v>0.0006836570675125417</v>
       </c>
       <c r="F35" t="n">
-        <v>0.04377540713572185</v>
+        <v>0.02614683666359167</v>
       </c>
       <c r="G35" t="n">
-        <v>49.31135257773587</v>
+        <v>31.70700593216975</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09283352109502048</v>
+        <v>0.03697885286041502</v>
       </c>
       <c r="I35" t="n">
-        <v>-107.4046902087683</v>
+        <v>-129.0491367163936</v>
       </c>
       <c r="J35" t="n">
-        <v>-94.87042095608726</v>
+        <v>-116.5148674637126</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1995,34 +1964,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.5641875820571072</v>
+        <v>0.444392318723815</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08140493220742497</v>
+        <v>0.08964817805431251</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01857739953566509</v>
+        <v>0.02368391871179926</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1362989344626916</v>
+        <v>0.1538958047244929</v>
       </c>
       <c r="G36" t="n">
-        <v>50.29361203499592</v>
+        <v>58.62497409580645</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1497479050578334</v>
+        <v>0.189261047481115</v>
       </c>
       <c r="I36" t="n">
-        <v>-83.61685692652858</v>
+        <v>-77.05989290597201</v>
       </c>
       <c r="J36" t="n">
-        <v>-68.06681453447663</v>
+        <v>-61.50985051392006</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>induction_qP</t>
+          <t>induction_rP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2031,244 +2000,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.4100531508899652</v>
+        <v>0.4883510814881357</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1494199258929221</v>
+        <v>0.09503641470561329</v>
       </c>
       <c r="E37" t="n">
-        <v>0.05325149768008318</v>
+        <v>0.01932272636670118</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2307628602701985</v>
+        <v>0.1390062098134511</v>
       </c>
       <c r="G37" t="n">
-        <v>91.76513886233147</v>
+        <v>63.99285035362388</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9325839872860957</v>
+        <v>0.1730205840102502</v>
       </c>
       <c r="I37" t="n">
-        <v>-49.31823373351361</v>
+        <v>-74.66183359662128</v>
       </c>
       <c r="J37" t="n">
-        <v>-34.6917238350952</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>BR02</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.6451944888413121</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.2453527026388743</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.1652203380268609</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.4064730471099663</v>
-      </c>
-      <c r="G38" t="n">
-        <v>79.24936105555602</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.228095889966409</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-6.608080336812073</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.390479791862525</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BR03</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>-4.748439183636087</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.7763954847524154</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.283402865222053</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.51109326820751</v>
-      </c>
-      <c r="G39" t="n">
-        <v>216.3068701343592</v>
-      </c>
-      <c r="H39" t="n">
-        <v>6.657827521492527</v>
-      </c>
-      <c r="I39" t="n">
-        <v>36.38500222596662</v>
-      </c>
-      <c r="J39" t="n">
-        <v>44.88160463919314</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>BR04</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.9734808402279989</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.008174724025868663</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.000348131281669426</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.01865827649246913</v>
-      </c>
-      <c r="G40" t="n">
-        <v>18.10382116191152</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.01419943982876894</v>
-      </c>
-      <c r="I40" t="n">
-        <v>-143.2215489662075</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-130.6872797135264</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>BR05</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.9415712352880893</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.007512055988646149</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.0003929002064510812</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.01982171048247555</v>
-      </c>
-      <c r="G41" t="n">
-        <v>14.71304895593737</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.02380365955808898</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-140.681053024855</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-128.146783772174</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>BR07</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.6277334277887661</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.07321103709252057</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.01586862732912495</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.1259707399721259</v>
-      </c>
-      <c r="G42" t="n">
-        <v>45.69831734977994</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.1287880107937577</v>
-      </c>
-      <c r="I42" t="n">
-        <v>-87.87210355786321</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-72.32206116581126</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>induction_rP</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0.8341141269535439</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.04566264031759223</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.006264778868879159</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.07915035608813872</v>
-      </c>
-      <c r="G43" t="n">
-        <v>39.09883312053942</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.06015110712215224</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-102.8202996881331</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-88.1937897897147</v>
+        <v>-60.03532369820287</v>
       </c>
     </row>
   </sheetData>
